--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,8 +431,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -483,6 +488,26 @@
           <t>couponDetailDisc</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>last_order_id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>last_used_cp</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>last_actual_price</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>last_updated</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,17 +523,12 @@
           <t xml:space="preserve">DC2608210007 </t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,17 +544,12 @@
           <t xml:space="preserve">DC2607310017 </t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46235</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,16 +560,358 @@
       <c r="B4" t="n">
         <v>143</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2609141SRMKUEH</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>141</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:53:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SP2-001713</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>300</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>300</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SP2-001714</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>300</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>300</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SP2-001715</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>301</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>301</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SP2-001716</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>301</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>301</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SP1-001579</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1404</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2609141P1CYP3G</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DC2609140008</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1404</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:51:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SP2-001610</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>311</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>311</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SP2-001611</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>310</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>310</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SP2-001612</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>310</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>310</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SP2-001613</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>311</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>311</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SP2-001753</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>390</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2609141KA8DDEA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>390</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:05:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SP2-001755</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>594</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2609141KA8DDEA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>594</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:05:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SV0-000101</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>260913VG3M2JV0</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:24:53</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -898,15 +898,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>260913VG3M2JV0</t>
+          <t>2609166YD777JH</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-14 15:24:53</t>
+          <t>2026-09-16 14:33:32</t>
         </is>
       </c>
     </row>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$P$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,16 @@
           <t>last_updated</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>last_adjustment_method</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_cp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -910,8 +920,236 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MNL-002435</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2737</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2609251AWCE1CK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CP2609160013 DC2608280030</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>2737</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:59:46</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9036</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SP2-001858+SP2-001859</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SP2-001778+SP2-001779</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>832</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CP2609040007 DC2609170010</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9673</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SP4-000302</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11997</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SP2-001869+SP2-001870</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SP2-001858+SP2-001859</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1861</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>955</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,21 @@
           <t>suggested_cp</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_usage_start_date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_usage_end_date</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_remark</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1001,155 +1016,200 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9673</v>
+        <v>141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>141</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
+        <v>903</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11997</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>903</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1849</v>
+        <v>1861</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1241</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1234</v>
+        <v>955</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1861</v>
+        <v>9673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DC2608310029 DC2609140003</t>
+          <t>CP2609090005</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1017</v>
+        <v>11997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>950</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1449</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>955</v>
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1449</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>หมายเหตุ : Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:S33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -923,15 +923,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2609166YD777JH</t>
+          <t>260929A9FF4P5G</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-16 14:33:32</t>
+          <t>2026-10-01 11:11:03</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>OC</t>
         </is>
       </c>
     </row>
@@ -991,181 +996,296 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>832</v>
+        <v>141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CP2609040007 DC2609170010</t>
+          <t>DC2609220006</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>141</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
+        <v>903</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>903</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1849</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1241</v>
+        <v>1861</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1861</v>
+        <v>9673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DC2608310029 DC2609140003</t>
+          <t>CP2609090005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>950</v>
+        <v>832</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>955</v>
+        <v>794</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>PR5-000661</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9673</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
+        <v>8602</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11997</v>
+        <v>9551</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1017</v>
+        <v>11997</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1199</v>
+        <v>2931</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1177,39 +1297,299 @@
       <c r="B32" t="n">
         <v>1234</v>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>950</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1199</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B35" t="n">
         <v>1449</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:50:55</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>CP2609220007</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>หมายเหตุ : Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1017</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:51:48</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>955</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:53:19</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1477</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:57:20</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>969</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:58:29</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>974</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:59:34</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S33"/>
+  <autoFilter ref="A1:S40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -1381,15 +1381,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1449</v>
+        <v>1017</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-01 11:50:55</t>
+          <t>2026-10-01 11:51:48</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -1409,27 +1409,27 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1017</v>
+        <v>955</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:51:48</t>
+          <t>2026-10-01 11:53:19</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -1444,62 +1444,62 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>955</v>
+        <v>1477</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-01 11:53:19</t>
+          <t>2026-10-01 11:57:20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1477</v>
+        <v>969</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:57:20</t>
+          <t>2026-10-01 11:58:29</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -1514,22 +1514,22 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-01 11:58:29</t>
+          <t>2026-10-01 11:59:34</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -1549,42 +1549,42 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>974</v>
+        <v>1449</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-01 11:59:34</t>
+          <t>2026-10-01 17:06:31</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>09/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
         </is>
       </c>
     </row>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1588,8 +1588,140 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SP2-001792</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>363</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>363</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:58:23</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SP2-001793</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>362</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>362</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:58:23</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SP2-001794</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>362</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>362</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:58:23</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SP2-001795</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>362</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>362</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:58:23</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S40"/>
+  <autoFilter ref="A1:S44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -9,17 +9,16 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$44</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,11 +429,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -548,12 +543,26 @@
           <t xml:space="preserve">DC2608210007 </t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>46258</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="2" t="n">
         <v>46273</v>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,12 +578,26 @@
           <t xml:space="preserve">DC2607310017 </t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>46273</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -585,6 +608,14 @@
       <c r="B4" t="n">
         <v>143</v>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>2609141SRMKUEH</t>
@@ -603,6 +634,11 @@
           <t>2026-09-14 14:53:23</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -613,6 +649,14 @@
       <c r="B5" t="n">
         <v>300</v>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -631,6 +675,11 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -641,6 +690,14 @@
       <c r="B6" t="n">
         <v>300</v>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -659,6 +716,11 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -669,6 +731,14 @@
       <c r="B7" t="n">
         <v>301</v>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -687,6 +757,11 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,6 +772,14 @@
       <c r="B8" t="n">
         <v>301</v>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -715,6 +798,11 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -725,6 +813,14 @@
       <c r="B9" t="n">
         <v>1404</v>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>2609141P1CYP3G</t>
@@ -743,6 +839,11 @@
           <t>2026-09-14 14:51:36</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -753,6 +854,14 @@
       <c r="B10" t="n">
         <v>311</v>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -771,6 +880,11 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -781,6 +895,14 @@
       <c r="B11" t="n">
         <v>310</v>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -799,6 +921,11 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -809,6 +936,14 @@
       <c r="B12" t="n">
         <v>310</v>
       </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -827,6 +962,11 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -837,6 +977,14 @@
       <c r="B13" t="n">
         <v>311</v>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -855,6 +1003,11 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -865,6 +1018,14 @@
       <c r="B14" t="n">
         <v>390</v>
       </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>2609141KA8DDEA</t>
@@ -883,6 +1044,11 @@
           <t>2026-09-14 15:05:24</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,6 +1059,14 @@
       <c r="B15" t="n">
         <v>594</v>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>2609141KA8DDEA</t>
@@ -911,6 +1085,11 @@
           <t>2026-09-14 15:05:24</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -921,11 +1100,20 @@
       <c r="B16" t="n">
         <v>4</v>
       </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>260929A9FF4P5G</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>4</v>
       </c>
@@ -939,6 +1127,10 @@
           <t>OC</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -949,6 +1141,14 @@
       <c r="B17" t="n">
         <v>2737</v>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>2609251AWCE1CK</t>
@@ -972,6 +1172,10 @@
           <t>OC</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -982,6 +1186,23 @@
       <c r="B18" t="n">
         <v>9036</v>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -992,6 +1213,23 @@
       <c r="B19" t="n">
         <v>1820</v>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1002,6 +1240,7 @@
       <c r="B20" t="n">
         <v>141</v>
       </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>23/09/2026</t>
@@ -1012,11 +1251,24 @@
           <t>09/10/2026</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>DC2609220006</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1027,6 +1279,23 @@
       <c r="B21" t="n">
         <v>903</v>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1037,6 +1306,23 @@
       <c r="B22" t="n">
         <v>1849</v>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1047,6 +1333,23 @@
       <c r="B23" t="n">
         <v>1241</v>
       </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1057,6 +1360,7 @@
       <c r="B24" t="n">
         <v>1861</v>
       </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>14/09/2026</t>
@@ -1067,11 +1371,24 @@
           <t>30/09/2026</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>DC2608310029 DC2609140003</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1082,6 +1399,7 @@
       <c r="B25" t="n">
         <v>9673</v>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>09/09/2026</t>
@@ -1092,11 +1410,24 @@
           <t>08/10/2026</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CP2609090005</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1107,6 +1438,7 @@
       <c r="B26" t="n">
         <v>832</v>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>18/09/2026</t>
@@ -1117,6 +1449,16 @@
           <t>08/10/2026</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>DC2609220002</t>
@@ -1147,6 +1489,19 @@
       <c r="B27" t="n">
         <v>794</v>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>DC2609220002</t>
@@ -1177,6 +1532,19 @@
       <c r="B28" t="n">
         <v>8602</v>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1207,6 +1575,19 @@
       <c r="B29" t="n">
         <v>9551</v>
       </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1237,6 +1618,19 @@
       <c r="B30" t="n">
         <v>11997</v>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1267,6 +1661,19 @@
       <c r="B31" t="n">
         <v>2931</v>
       </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1297,6 +1704,19 @@
       <c r="B32" t="n">
         <v>1234</v>
       </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1327,6 +1747,19 @@
       <c r="B33" t="n">
         <v>950</v>
       </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1357,6 +1790,19 @@
       <c r="B34" t="n">
         <v>1199</v>
       </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>DC2609220006</t>
@@ -1387,11 +1833,23 @@
       <c r="B35" t="n">
         <v>1017</v>
       </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>2026-10-01 11:51:48</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1422,11 +1880,23 @@
       <c r="B36" t="n">
         <v>955</v>
       </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>2026-10-01 11:53:19</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1457,11 +1927,23 @@
       <c r="B37" t="n">
         <v>1477</v>
       </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>2026-10-01 11:57:20</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CP2609300040</t>
@@ -1492,11 +1974,23 @@
       <c r="B38" t="n">
         <v>969</v>
       </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>2026-10-01 11:58:29</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>CP2609290081</t>
@@ -1527,11 +2021,23 @@
       <c r="B39" t="n">
         <v>974</v>
       </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>2026-10-01 11:59:34</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>CP2609290081</t>
@@ -1562,11 +2068,23 @@
       <c r="B40" t="n">
         <v>1449</v>
       </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>2026-10-01 17:06:31</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1588,140 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SP2-001792</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>363</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>363</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:58:23</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SP2-001793</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>362</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>362</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:58:23</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SP2-001794</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>362</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>362</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:58:23</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SP2-001795</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>362</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>362</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:58:23</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,11 +1094,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SV0-000101</t>
+          <t>MNL-002435</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2737</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -1110,16 +1110,20 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>260929A9FF4P5G</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2609251AWCE1CK</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CP2609160013 DC2608280030</t>
+        </is>
+      </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>2737</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-01 11:11:03</t>
+          <t>2026-09-29 14:59:46</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1135,11 +1139,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MNL-002435</t>
+          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2737</v>
+        <v>9036</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -1149,29 +1153,11 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2609251AWCE1CK</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>CP2609160013 DC2608280030</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>2737</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:59:46</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>OC</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1180,11 +1166,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9036</v>
+        <v>1820</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -1207,15 +1193,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1820</v>
+        <v>141</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1226,7 +1220,11 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -1234,23 +1232,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141</v>
+        <v>903</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1261,11 +1251,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -1273,11 +1259,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>903</v>
+        <v>1849</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1300,11 +1286,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1849</v>
+        <v>1241</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1327,15 +1313,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1241</v>
+        <v>1861</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1346,7 +1340,11 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -1354,21 +1352,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1861</v>
+        <v>9673</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1383,7 +1381,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DC2608310029 DC2609140003</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -1393,16 +1391,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9673</v>
+        <v>832</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1422,33 +1420,37 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>832</v>
+        <v>794</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1476,18 +1478,18 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>PR5-000661</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>794</v>
+        <v>8602</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1504,33 +1506,33 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PR5-000661</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8602</v>
+        <v>9551</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1552,28 +1554,28 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9551</v>
+        <v>11997</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1590,7 +1592,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -1605,18 +1607,18 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11997</v>
+        <v>2931</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -1633,7 +1635,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -1648,18 +1650,18 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2931</v>
+        <v>1234</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1676,7 +1678,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -1691,18 +1693,18 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1234</v>
+        <v>950</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -1719,7 +1721,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -1734,18 +1736,18 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>950</v>
+        <v>1199</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1762,7 +1764,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>DC2609220006</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -1777,18 +1779,18 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1199</v>
+        <v>1017</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -1801,11 +1803,15 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:51:48</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -1820,18 +1826,18 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1017</v>
+        <v>955</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -1846,13 +1852,13 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-01 11:51:48</t>
+          <t>2026-10-01 11:53:19</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -1867,18 +1873,18 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>955</v>
+        <v>1477</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -1893,39 +1899,39 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:53:19</t>
+          <t>2026-10-01 11:57:20</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1477</v>
+        <v>969</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -1940,13 +1946,13 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-01 11:57:20</t>
+          <t>2026-10-01 11:58:29</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -1961,18 +1967,18 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -1987,7 +1993,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:58:29</t>
+          <t>2026-10-01 11:59:34</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -2008,18 +2014,18 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>974</v>
+        <v>1449</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -2034,73 +2040,26 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-01 11:59:34</t>
+          <t>2026-10-01 17:06:31</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>09/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1449</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:06:31</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>23/09/2026 00:00:01</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>09/10/2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
         <is>
           <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
         </is>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$55</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,8 +431,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -543,26 +548,12 @@
           <t xml:space="preserve">DC2608210007 </t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46258</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,26 +569,12 @@
           <t xml:space="preserve">DC2607310017 </t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46235</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -608,14 +585,6 @@
       <c r="B4" t="n">
         <v>143</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>2609141SRMKUEH</t>
@@ -634,11 +603,6 @@
           <t>2026-09-14 14:53:23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,14 +613,6 @@
       <c r="B5" t="n">
         <v>300</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -675,11 +631,6 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -690,14 +641,6 @@
       <c r="B6" t="n">
         <v>300</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -716,11 +659,6 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -731,14 +669,6 @@
       <c r="B7" t="n">
         <v>301</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -757,11 +687,6 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -772,14 +697,6 @@
       <c r="B8" t="n">
         <v>301</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>2609141MCF7RSD</t>
@@ -798,11 +715,6 @@
           <t>2026-09-14 14:48:42</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -813,14 +725,6 @@
       <c r="B9" t="n">
         <v>1404</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>2609141P1CYP3G</t>
@@ -839,11 +743,6 @@
           <t>2026-09-14 14:51:36</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -854,14 +753,6 @@
       <c r="B10" t="n">
         <v>311</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -880,11 +771,6 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -895,14 +781,6 @@
       <c r="B11" t="n">
         <v>310</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -921,11 +799,6 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -936,14 +809,6 @@
       <c r="B12" t="n">
         <v>310</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -962,11 +827,6 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -977,14 +837,6 @@
       <c r="B13" t="n">
         <v>311</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>2609141P4RQJXW</t>
@@ -1003,11 +855,6 @@
           <t>2026-09-14 14:57:10</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1018,14 +865,6 @@
       <c r="B14" t="n">
         <v>390</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>2609141KA8DDEA</t>
@@ -1044,11 +883,6 @@
           <t>2026-09-14 15:05:24</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1059,14 +893,6 @@
       <c r="B15" t="n">
         <v>594</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>2609141KA8DDEA</t>
@@ -1085,11 +911,6 @@
           <t>2026-09-14 15:05:24</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1100,14 +921,6 @@
       <c r="B16" t="n">
         <v>2737</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>2609251AWCE1CK</t>
@@ -1131,10 +944,6 @@
           <t>OC</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1145,23 +954,6 @@
       <c r="B17" t="n">
         <v>9036</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1172,23 +964,6 @@
       <c r="B18" t="n">
         <v>1820</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1199,7 +974,6 @@
       <c r="B19" t="n">
         <v>141</v>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>23/09/2026</t>
@@ -1210,24 +984,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>DC2609220006</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1238,23 +999,6 @@
       <c r="B20" t="n">
         <v>903</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1265,23 +1009,6 @@
       <c r="B21" t="n">
         <v>1849</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1292,23 +1019,6 @@
       <c r="B22" t="n">
         <v>1241</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1319,7 +1029,6 @@
       <c r="B23" t="n">
         <v>1861</v>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>14/09/2026</t>
@@ -1330,94 +1039,81 @@
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>DC2608310029 DC2609140003</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9673</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>832</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>832</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>794</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>DC2609220002</t>
@@ -1435,118 +1131,124 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>PR5-000661</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>794</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+        <v>8602</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PR5-000661</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8602</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+        <v>11997</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9551</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+        <v>2931</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1564,32 +1266,34 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11997</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+        <v>1234</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1607,32 +1311,34 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2931</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+        <v>950</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1650,32 +1356,57 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1234</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+        <v>1017</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>260930DC4DT2CY</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1017</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:00:19</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>CP2609220007</t>
@@ -1693,32 +1424,57 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>950</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+        <v>955</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>260930DWC0FFR9</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>955</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:18:21</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>CP2609220002</t>
@@ -1736,97 +1492,143 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1199</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+        <v>1477</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>261001FGRN0E3U</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1477</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:23:56</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1017</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+        <v>969</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>261001G5NXM272</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>969</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-01 11:51:48</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>2026-10-02 17:51:08</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
         </is>
       </c>
     </row>
@@ -1837,43 +1639,64 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>955</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+        <v>974</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>261002HSQNAN0G</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>974</v>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-01 11:53:19</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>2026-10-02 18:01:03</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>23/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
@@ -1884,188 +1707,1112 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1477</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+        <v>1449</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1449</v>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:57:20</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>2026-10-02 15:52:56</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>23/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>09/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>969</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+        <v>1566</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2609288A3EJJGE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1566</v>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-01 11:58:29</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>2026-10-02 16:15:10</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 1566</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP1-001210</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>974</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+        <v>1412</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>260929AW9BRK4J</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1412</v>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:59:34</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>2026-10-02 16:15:43</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 1412</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP4-000241</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1449</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DC2608280023</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>DC2608280023</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>400</v>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-01 17:06:31</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2608280023</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Shp Lzd TT ราคา400</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SP4-000076</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>640</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>261001GGR265EJ</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>590</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:54:59</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>9551</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>23/09/2026 00:00:01</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>09/10/2026 23:59:59</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>260930D84RADEG</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>9551</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:17:19</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1199</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>260930DWC0FFR9</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1199</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:18:21</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>23/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SP4-000241</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>405</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>261001EXVBHTNJ</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>405</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:20:06</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 405</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SP4-000302</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>139</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>261002HNMRU6N2</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>139</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:59:34</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MS2-000754</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>375</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>375</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MS2-000820</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>225</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>225</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MS2-000942</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>450</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>450</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SP1-001378</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3031</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:21:12</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 3031</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:25:26</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9673</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>09/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>08/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>261001FNX3QHKT</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>9673</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:47:09</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>09/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>08/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Dynamic ก.ย. Shp ราคา 9673</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>261002HMFAY2EQ</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>1056</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:58:55</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 409</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MNL-002445</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2847</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>261001FVHQUH0S</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>2847</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:32:59</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SP1-001210</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1446</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>261001FX5EERNK</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1446</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:48:15</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1446</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SP1-001113</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>261002HSH1MCYP</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>1603</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:00:21</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SP4-000196</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>305</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:42:36</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2445,9 +2445,27 @@
           <t>31/10/2026 23:59:59</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>261003ND0STEU0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1280</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-02 16:25:26</t>
+          <t>2026-10-05 10:38:45</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -2565,7 +2583,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>261002HMFAY2EQ</t>
+          <t>261002JEPP9507</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -2578,7 +2596,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-02 17:58:55</t>
+          <t>2026-10-05 10:37:22</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -2811,8 +2829,23 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>993</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:37:56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S55"/>
+  <autoFilter ref="A1:S56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>261001FGRN0E3U</t>
+          <t>261004QX1BTQAW</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-02 16:23:56</t>
+          <t>2026-10-05 15:15:04</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>261001G5NXM272</t>
+          <t>261005SPK3PU2U</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-02 17:51:08</t>
+          <t>2026-10-05 15:36:58</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>261002HSQNAN0G</t>
+          <t>261005S1000PVF</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-02 18:01:03</t>
+          <t>2026-10-05 16:09:48</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>261001GGR265EJ</t>
+          <t>261005S561P3G2</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-02 17:54:59</t>
+          <t>2026-10-05 15:23:04</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>261001EXVBHTNJ</t>
+          <t>261005SGFV6AYU</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-02 16:20:06</t>
+          <t>2026-10-05 15:32:13</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>261002HNMRU6N2</t>
+          <t>261005SRV913UJ</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-02 17:59:34</t>
+          <t>2026-10-05 15:37:57</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -2395,9 +2395,27 @@
           <t>31/10/2026</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>261005SB6KAGSA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>3031</v>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-02 16:21:12</t>
+          <t>2026-10-05 15:28:13</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -2447,7 +2465,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>261003ND0STEU0</t>
+          <t>261005SEX8B805</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2460,7 +2478,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-05 10:38:45</t>
+          <t>2026-10-05 15:30:39</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -2596,7 +2614,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-05 10:37:22</t>
+          <t>2026-10-05 15:07:40</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -2684,7 +2702,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>261001FX5EERNK</t>
+          <t>261004PYNMBJ77</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -2697,7 +2715,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-02 17:48:15</t>
+          <t>2026-10-05 15:09:51</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -2803,6 +2821,21 @@
       <c r="B55" t="n">
         <v>305</v>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>2026-10-02 17:42:36</t>
@@ -2832,20 +2865,138 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1330</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DC2609290042</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DC2609290042</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>1330</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:09:48</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DC2609290042</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B57" t="n">
         <v>993</v>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2026-10-05 10:37:56</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>46279.00001157408</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>5 4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>261005SER9K7CC</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>993</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:34:34</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>CP + OC</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>FS Shp Rebate ราคาเซ็ทละ 993</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S56"/>
+  <autoFilter ref="A1:S57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>261005SPK3PU2U</t>
+          <t>261004R3TD9APG</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-05 15:36:58</t>
+          <t>2026-10-07 14:38:24</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2207,79 +2207,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>MS2-000754</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>139</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DC2609300024</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
+        <v>375</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>261005SRV913UJ</t>
+          <t>260929BD1UJHCV</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>139</v>
+        <v>375</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-05 15:37:57</t>
+          <t>2026-10-02 16:35:35</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>DC2609300024</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS2-000754</t>
+          <t>MS2-000820</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>375</v>
+        <v>225</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2292,7 +2257,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>375</v>
+        <v>225</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -2301,18 +2266,18 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>MANUAL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MS2-000820</t>
+          <t>MS2-000942</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2325,7 +2290,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2341,76 +2306,111 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MS2-000942</t>
+          <t>SP1-001378</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>450</v>
+        <v>3031</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>261005SB6KAGSA</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>450</v>
+        <v>3031</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-05 15:28:13</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 3031</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SP1-001378</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3031</v>
+        <v>1280</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>261005SB6KAGSA</t>
+          <t>261005SEX8B805</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3031</v>
+        <v>1280</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-05 15:28:13</t>
+          <t>2026-10-05 15:30:39</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -2420,65 +2420,65 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 3031</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1280</v>
+        <v>9673</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>09/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>08/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>261005SEX8B805</t>
+          <t>261001FNX3QHKT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1280</v>
+        <v>9673</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-05 15:30:39</t>
+          <t>2026-10-02 17:47:09</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -2488,65 +2488,65 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>09/09/2026 00:00:01</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>08/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
+          <t>Dynamic ก.ย. Shp ราคา 9673</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9673</v>
+        <v>1056</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08/10/2026 23:59:59</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>261001FNX3QHKT</t>
+          <t>261002JEPP9507</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>9673</v>
+        <v>1056</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-02 17:47:09</t>
+          <t>2026-10-07 14:36:59</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -2556,134 +2556,129 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>09/09/2026 00:00:01</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>08/10/2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Dynamic ก.ย. Shp ราคา 9673</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>MNL-002445</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1056</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CP2609300040</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>01/10/2026 00:00:01</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>31/10/2026 23:59:59</t>
-        </is>
+        <v>2847</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>261002JEPP9507</t>
+          <t>261001FVHQUH0S</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2609280021 DC2609280008</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1056</v>
+        <v>2847</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-05 15:07:40</t>
+          <t>2026-10-02 16:32:59</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>CP2609300040</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>01/10/2026 00:00:01</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>31/10/2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 409</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MNL-002445</t>
+          <t>SP1-001210</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2847</v>
+        <v>1446</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>261001FVHQUH0S</t>
+          <t>261004PYNMBJ77</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>2847</v>
+        <v>1446</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-02 16:32:59</t>
+          <t>2026-10-05 15:09:51</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1446</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SP1-001210</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1446</v>
+        <v>1603</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2702,7 +2697,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>261004PYNMBJ77</t>
+          <t>261002HSH1MCYP</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -2711,11 +2706,11 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1446</v>
+        <v>1603</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-05 15:09:51</t>
+          <t>2026-10-02 18:00:21</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -2740,22 +2735,22 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 1446</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SP1-001113</t>
+          <t>SP4-000196</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1603</v>
+        <v>305</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2768,32 +2763,14 @@
           <t>31/10/2026</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>261002HSH1MCYP</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>1603</v>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-02 18:00:21</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-02 17:42:36</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -2808,180 +2785,198 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SP4-000196</t>
+          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>305</v>
+        <v>1330</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
+          <t>DC2609290042</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>261005S1000PVF</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DC2609290042</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>1330</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-02 17:42:36</t>
+          <t>2026-10-05 16:09:48</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2609290042</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>31/10/2026 23:59:59</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1330</v>
+        <v>993</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46279.00001157408</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46304</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5 4</t>
+        </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>261005S1000PVF</t>
+          <t>261003K6J8B8H5</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1330</v>
+        <v>993</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-05 16:09:48</t>
+          <t>2026-10-07 14:37:38</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>CP + OC</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2610050027</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>01/10/2026 00:00:01</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>31/10/2026 23:59:59</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
+          <t>FS Shp Rebate ราคาเซ็ทละ 993</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>993</v>
+        <v>139</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>46279.00001157408</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>5 4</t>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>261005SER9K7CC</t>
+          <t>261005SRV913UJ</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>993</v>
+        <v>139</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-05 16:34:34</t>
+          <t>2026-10-07 14:39:21</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>CP + OC</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -2991,7 +2986,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>FS Shp Rebate ราคาเซ็ทละ 993</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
         </is>
       </c>
     </row>

--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>261002JEPP9507</t>
+          <t>261007265U804D</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-08 10:37:00</t>
+          <t>2026-10-08 11:11:26</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2610071GF09EGA</t>
+          <t>2610071YKH3P16</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-08 10:50:44</t>
+          <t>2026-10-08 11:07:28</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46296</v>
+        <v>46032</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>46326</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-08 10:53:27</t>
+          <t>2026-10-08 11:09:55</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2610071KFTTTYK</t>
+          <t>26100729P4PHTQ</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-08 10:55:47</t>
+          <t>2026-10-08 11:15:29</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -869,17 +869,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-08 10:54:58</t>
+          <t>2026-10-08 11:13:37</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>CP + OC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>CP2610050027</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n">
@@ -888,11 +883,6 @@
       <c r="R7" s="3" t="n">
         <v>46337.99998842592</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -916,7 +906,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2610071HRU9UPY</t>
+          <t>2610071PP00HWD</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -929,7 +919,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-08 10:52:36</t>
+          <t>2026-10-08 11:00:07</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -976,7 +966,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>261006V0FBP040</t>
+          <t>2610072A0U120S</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -989,7 +979,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-08 10:33:43</t>
+          <t>2026-10-08 11:17:02</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,14 +1289,14 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46296</v>
+        <v>46032</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26100717549GJX</t>
+          <t>2610071MEQQ7CT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1319,7 +1309,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-08 10:38:43</t>
+          <t>2026-10-08 10:58:32</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1333,7 +1323,7 @@
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>46296</v>
+        <v>46032</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>46326</v>
@@ -1347,887 +1337,799 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>137</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC2608210007 </t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46273</v>
+        <v>2993</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:59:18</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2993</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SP4-000242</t>
+          <t>TEST-PATTERN-SKU</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>860</v>
+        <v>999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC2607310017 </t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46243</v>
+          <t>CP_INSERTED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>08/10/2026 11:09:23</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>TEST-PATTERN-SKU-2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>143</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2609141SRMKUEH</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>DC2609140005</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>141</v>
+        <v>999</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CP_NEW</t>
+        </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-14 14:53:23</t>
+          <t>08/10/2026 11:02:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SP2-001713</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>300</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2609141MCF7RSD</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>DC2609140005</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>300</v>
+        <v>921</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-10-08 11:04:54</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 921</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP2-001714</t>
+          <t>SP1-001449</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>300</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2609141MCF7RSD</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>DC2609140005</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>300</v>
+        <v>2220</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46336</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-10-08 11:05:23</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46336</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 2220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SP2-001715</t>
+          <t>TEST-PATTERN-SKU</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>301</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2609141MCF7RSD</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>DC2609140005</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>301</v>
+        <v>888</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CP_NEW_PRICE</t>
+        </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>08/10/2026 11:06:56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP2-001716</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>301</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2609141MCF7RSD</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>DC2609140005</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>301</v>
+        <v>851</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-10-08 11:09:24</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP1-001579</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1404</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2609141P1CYP3G</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>DC2609140008</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>1404</v>
+        <v>810</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-14 14:51:36</t>
+          <t>2026-10-08 11:10:32</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP2-001610</t>
+          <t>MS2-000818</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>311</v>
+        <v>225</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2609141P4RQJXW</t>
+          <t>261007288HJTKT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:10</t>
+          <t>2026-10-08 11:12:30</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001611</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>310</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2609141P4RQJXW</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>310</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-09-14 14:57:10</t>
-        </is>
+        <v>137</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DC2608210007</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46273</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP2-001612</t>
+          <t>SP4-000242</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>310</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2609141P4RQJXW</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>310</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2026-09-14 14:57:10</t>
-        </is>
+        <v>860</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DC2607310017</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46273</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP2-001613</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>311</v>
+        <v>143</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2609141P4RQJXW</t>
+          <t>2609141SRMKUEH</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>DC2609140005</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>311</v>
+        <v>141</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:10</t>
+          <t>2026-09-14 14:53:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>SP2-001713</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2609141KA8DDEA</t>
+          <t>2609141MCF7RSD</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>DC2609140005</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-14 15:05:24</t>
+          <t>2026-09-14 14:48:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001755</t>
+          <t>SP2-001714</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>594</v>
+        <v>300</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2609141KA8DDEA</t>
+          <t>2609141MCF7RSD</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>DC2609140005</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>594</v>
+        <v>300</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-14 15:05:24</t>
+          <t>2026-09-14 14:48:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MNL-002435</t>
+          <t>SP2-001715</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2737</v>
+        <v>301</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2609251AWCE1CK</t>
+          <t>2609141MCF7RSD</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CP2609160013 DC2608280030</t>
+          <t>DC2609140005</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2737</v>
+        <v>301</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-29 14:59:46</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>OC</t>
+          <t>2026-09-14 14:48:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
+          <t>SP2-001716</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9036</v>
+        <v>301</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>301</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP1-001579</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1820</v>
+        <v>1404</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2609141P1CYP3G</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DC2609140008</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1404</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:51:36</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001610</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>141</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
+        <v>311</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>311</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>SP2-001611</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>903</v>
+        <v>310</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>310</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001612</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1241</v>
+        <v>310</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>310</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP2-001613</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1861</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DC2608310029 DC2609140003</t>
+        <v>311</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2609141P4RQJXW</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>311</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>832</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+        <v>390</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2609141KA8DDEA</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>390</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:05:24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>SP2-001755</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>794</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
+        <v>594</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2609141KA8DDEA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>594</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:05:24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PR5-000661</t>
+          <t>MNL-002435</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8602</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
+        <v>2737</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2609251AWCE1CK</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CP2609160013 DC2608280030</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>2737</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:59:46</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11997</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
-        </is>
+        <v>9036</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2931</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
-        </is>
+        <v>1820</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1234</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
+        <v>141</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46304</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
+          <t>DC2609220006</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>950</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
-        </is>
+        <v>903</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1017</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>260930DC4DT2CY</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>1017</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:00:19</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
-        </is>
+        <v>1241</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>955</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
+        <v>1861</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46279</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>260930DWC0FFR9</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
-        <v>955</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:18:21</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
+        <v>46295</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+          <t>DC2608310029 DC2609140003</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1449</v>
+        <v>832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -2236,32 +2138,9 @@
       <c r="E47" s="3" t="n">
         <v>46304.99998842592</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2609287HFYKV3U</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>CP2609220007</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
-        <v>1449</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-10-02 15:52:56</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q47" s="3" t="n">
@@ -2272,18 +2151,18 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SP1-001113</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1566</v>
+        <v>794</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2291,63 +2170,40 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2609288A3EJJGE</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>DC2609220002</t>
         </is>
       </c>
-      <c r="M48" t="n">
-        <v>1566</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:15:10</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
       <c r="Q48" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 1566</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SP1-001210</t>
+          <t>PR5-000661</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1412</v>
+        <v>8602</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -2356,32 +2212,9 @@
       <c r="E49" s="3" t="n">
         <v>46304</v>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>260929AW9BRK4J</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
-        <v>1412</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:15:43</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q49" s="3" t="n">
@@ -2392,110 +2225,96 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 1412</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SP4-000241</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>400</v>
+        <v>11997</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DC2608280023</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>46266</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>260929BD1UJHCV</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>DC2608280023</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>400</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:35:35</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
+        <v>46304.99998842592</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>DC2608280023</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>46266</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="R50" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Shp Lzd TT ราคา400</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SP4-000076</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>640</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2610071JEP9U3K</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>590</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2026-10-08 10:54:25</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>OC</t>
+        <v>2931</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9551</v>
+        <v>1234</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -2504,32 +2323,9 @@
       <c r="E52" s="3" t="n">
         <v>46304.99998842592</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>260930D84RADEG</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>9551</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:17:19</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q52" s="3" t="n">
@@ -2540,22 +2336,22 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1199</v>
+        <v>950</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -2564,32 +2360,9 @@
       <c r="E53" s="3" t="n">
         <v>46304.99998842592</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>260930DWC0FFR9</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>1199</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:18:21</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q53" s="3" t="n">
@@ -2600,145 +2373,226 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MS2-000754</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>375</v>
+        <v>1017</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46304.99998842592</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>260930DC4DT2CY</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>375</v>
+        <v>1017</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-02 16:00:19</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MS2-000820</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>225</v>
+        <v>955</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46304.99998842592</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>260930DWC0FFR9</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>225</v>
+        <v>955</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-02 16:18:21</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MS2-000942</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>450</v>
+        <v>1449</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46304.99998842592</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>2609287HFYKV3U</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>450</v>
+        <v>1449</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-02 15:52:56</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9673</v>
+        <v>1566</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>46274.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46304</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>261001FNX3QHKT</t>
+          <t>2609288A3EJJGE</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>9673</v>
+        <v>1566</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-02 17:47:09</t>
+          <t>2026-10-02 16:15:10</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -2748,116 +2602,746 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>46274.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46304</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Dynamic ก.ย. Shp ราคา 9673</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 1566</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MNL-002445</t>
+          <t>SP1-001210</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2847</v>
+        <v>1412</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>46304</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>261001FVHQUH0S</t>
+          <t>260929AW9BRK4J</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>2847</v>
+        <v>1412</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-02 16:32:59</t>
+          <t>2026-10-02 16:15:43</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคา 1412</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>SP4-000241</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>400</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DC2608280023</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DC2608280023</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>400</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DC2608280023</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Shp Lzd TT ราคา400</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SP4-000076</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>640</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2610071JEP9U3K</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>590</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:54:25</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>9551</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>260930D84RADEG</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>9551</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:17:19</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1199</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>260930DWC0FFR9</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>1199</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:18:21</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MS2-000754</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>375</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>375</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MS2-000820</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>225</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>225</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MS2-000942</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>450</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>450</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:35:35</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>9673</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46274.00001157408</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46303.99998842592</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>261001FNX3QHKT</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>9673</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:47:09</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>CP2609090005</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>46274.00001157408</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46303.99998842592</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Dynamic ก.ย. Shp ราคา 9673</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MNL-002445</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2847</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>261001FVHQUH0S</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>2847</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:32:59</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>SP1-001113</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B68" t="n">
         <v>1603</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>DC2609290041</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D68" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>261002HSH1MCYP</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>1603</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:00:21</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SP1-001449</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2220</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:05:23</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="n">
         <v>46296</v>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>261002HSH1MCYP</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
+      <c r="R69" s="3" t="n">
+        <v>46336</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 2220</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SP2-001778+SP2-001779</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>851</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:09:24</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>DC2609290041</t>
         </is>
       </c>
-      <c r="M59" t="n">
-        <v>1603</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2026-10-02 18:00:21</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="Q70" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SP2-001607+SP2-001754</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>810</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:10:32</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MS2-000818</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>225</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>261007288HJTKT</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>225</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:12:30</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>CP</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R59" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>993</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46152.00001157408</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:13:20</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>46152.00001157408</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1052</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:16:15</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>07/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>20/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซ็ทละ 1052</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S59"/>
+  <autoFilter ref="A1:S74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>261007265U804D</t>
+          <t>2610083HW7WMDS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-08 11:11:26</t>
+          <t>2026-10-08 11:29:33</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -588,6 +588,11 @@
       <c r="R2" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1056</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -611,7 +616,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2610071YKH3P16</t>
+          <t>2610082Q1FEJVD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -624,7 +629,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-08 11:07:28</t>
+          <t>2026-10-08 11:23:58</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -712,39 +717,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139</v>
+        <v>974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46032</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>261005SRV913UJ</t>
+          <t>2610082M7WMJXX</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>139</v>
+        <v>974</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-08 11:09:55</t>
+          <t>2026-10-08 11:22:03</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -754,33 +759,33 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>46296</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>974</v>
+        <v>1477</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -791,20 +796,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>26100729P4PHTQ</t>
+          <t>2610083CRKVQ58</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>974</v>
+        <v>1477</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-08 11:15:29</t>
+          <t>2026-10-08 11:28:37</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -814,7 +819,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q6" s="3" t="n">
@@ -825,77 +830,82 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>993</v>
+        <v>969</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46279.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5 4</t>
-        </is>
+        <v>46326.99998842592</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>261003K6J8B8H5</t>
+          <t>2610072A84PSC3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>993</v>
+        <v>969</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-08 11:13:37</t>
+          <t>2026-10-08 11:18:01</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CP + OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>46300.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>46337.99998842592</v>
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1477</v>
+        <v>1330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290042</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -906,20 +916,20 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2610071PP00HWD</t>
+          <t>26100704X2FT1A</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290042</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1477</v>
+        <v>1330</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-08 11:00:07</t>
+          <t>2026-10-08 10:35:49</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -929,7 +939,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290042</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n">
@@ -940,106 +950,74 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP4-000076</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>969</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CP2609290081</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>590</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2610072A0U120S</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>CP2609290081</t>
+          <t>2610071JEP9U3K</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>969</v>
+        <v>590</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-08 11:17:02</t>
+          <t>2026-10-08 10:54:25</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>CP2609290081</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP1-001378</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1330</v>
+        <v>3031</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26100704X2FT1A</t>
+          <t>261005SB6KAGSA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1330</v>
+        <v>3031</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-08 10:35:49</t>
+          <t>2026-10-05 15:28:13</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1049,85 +1027,117 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 3031</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SP4-000076</t>
+          <t>SP4-000241</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>590</v>
+        <v>405</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46336</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2610071JEP9U3K</t>
+          <t>261006V8F25WXF</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>590</v>
+        <v>405</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-08 10:54:25</t>
+          <t>2026-10-08 10:34:53</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46336</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 405</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SP1-001378</t>
+          <t>SP4-000196</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3031</v>
+        <v>305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46296</v>
+        <v>46032</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>261005SB6KAGSA</t>
+          <t>2610071NYB574H</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3031</v>
+        <v>305</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-05 15:28:13</t>
+          <t>2026-10-08 11:46:06</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1137,179 +1147,151 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>46296</v>
+        <v>46032</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 3031</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SP4-000241</t>
+          <t>TEST-PATTERN-SKU</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>405</v>
+        <v>999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>261006V8F25WXF</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>405</v>
+          <t>CP_INSERTED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-08 10:34:53</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Shp+Lzd+Tiktok ราคา 405</t>
+          <t>08/10/2026 11:09:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>TEST-PATTERN-SKU-2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1849</v>
+        <v>999</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CP_NEW</t>
+        </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-08 10:36:36</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>CP2609210010</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>46286.00001157408</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>46303.99998842592</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Dynamic ก.ย. Shp ราคาเซท 1849</t>
+          <t>08/10/2026 11:02:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>952</v>
+        <v>921</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2610071V2MM04F</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>921</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-08 10:41:56</t>
+          <t>2026-10-08 11:50:02</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CP2610060006</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>46302.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>46315.99998842592</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>FS Shp ราคาเซท 952</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 921</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SP4-000196</t>
+          <t>SP1-001449</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>305</v>
+        <v>2220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46032</v>
+        <v>46296</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46326</v>
+        <v>46336</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2610071MEQQ7CT</t>
+          <t>2610071VPKHFM4</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>305</v>
+        <v>2220</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-08 10:58:32</t>
+          <t>2026-10-08 11:50:32</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1319,534 +1301,561 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>46032</v>
+        <v>46296</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>46326</v>
+        <v>46336</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
+          <t>Shp+Lzd+Tiktok ราคา 2220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+          <t>TEST-PATTERN-SKU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2993</v>
+        <v>888</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CP_NEW_PRICE</t>
+        </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-08 10:59:18</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>CP2609290081</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 2993</t>
+          <t>08/10/2026 11:06:56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEST-PATTERN-SKU</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>999</v>
+        <v>851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CP_INSERTED</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>26100839JAVCJ8</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>851</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>08/10/2026 11:09:23</t>
+          <t>2026-10-08 11:26:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEST-PATTERN-SKU-2</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>999</v>
+        <v>810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CP_NEW</t>
-        </is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2610072GWE2YKY</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>810</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>08/10/2026 11:02:06</t>
+          <t>2026-10-08 11:19:24</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>MS2-000818</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>921</v>
+        <v>225</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>261007288HJTKT</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>225</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-08 11:04:54</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 921</t>
+          <t>2026-10-08 11:12:30</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP1-001449</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2220</v>
+        <v>137</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
+          <t>DC2608210007</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46296</v>
+        <v>46258</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-10-08 11:05:23</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Shp+Lzd+Tiktok ราคา 2220</t>
-        </is>
+        <v>46273</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TEST-PATTERN-SKU</t>
+          <t>SP4-000242</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>888</v>
+        <v>860</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CP_NEW_PRICE</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>08/10/2026 11:06:56</t>
-        </is>
+          <t>DC2607310017</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>851</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>143</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2609141SRMKUEH</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>141</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-08 11:09:24</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
+          <t>2026-09-14 14:53:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>SP2-001713</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>810</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>300</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>300</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-08 11:10:32</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
+          <t>2026-09-14 14:48:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MS2-000818</t>
+          <t>SP2-001714</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CP2609290069 DC2609290002</t>
-        </is>
+        <v>300</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>261007288HJTKT</t>
+          <t>2609141MCF7RSD</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>DC2609140005</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-08 11:12:30</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-09-14 14:48:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001715</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>137</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DC2608210007</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46273</v>
+        <v>301</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>301</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP4-000242</t>
+          <t>SP2-001716</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>860</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DC2607310017</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46273</v>
+        <v>301</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2609141MCF7RSD</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DC2609140005</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>301</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:48:42</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP1-001579</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>143</v>
+        <v>1404</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2609141SRMKUEH</t>
+          <t>2609141P1CYP3G</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>DC2609140005</t>
+          <t>DC2609140008</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>141</v>
+        <v>1404</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-14 14:53:23</t>
+          <t>2026-09-14 14:51:36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP2-001713</t>
+          <t>SP2-001610</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2609141MCF7RSD</t>
+          <t>2609141P4RQJXW</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DC2609140005</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001714</t>
+          <t>SP2-001611</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2609141MCF7RSD</t>
+          <t>2609141P4RQJXW</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>DC2609140005</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001715</t>
+          <t>SP2-001612</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2609141MCF7RSD</t>
+          <t>2609141P4RQJXW</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DC2609140005</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP2-001716</t>
+          <t>SP2-001613</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2609141MCF7RSD</t>
+          <t>2609141P4RQJXW</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DC2609140005</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-14 14:48:42</t>
+          <t>2026-09-14 14:57:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP1-001579</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1404</v>
+        <v>390</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2609141P1CYP3G</t>
+          <t>2609141KA8DDEA</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>DC2609140008</t>
+          <t>CP2609140012</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1404</v>
+        <v>390</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-14 14:51:36</t>
+          <t>2026-09-14 15:05:24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP2-001610</t>
+          <t>SP2-001755</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>311</v>
+        <v>594</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2609141P4RQJXW</t>
+          <t>2609141KA8DDEA</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -1855,281 +1864,325 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>311</v>
+        <v>594</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:10</t>
+          <t>2026-09-14 15:05:24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP2-001611</t>
+          <t>MNL-002435</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>310</v>
+        <v>2737</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2609141P4RQJXW</t>
+          <t>2609251AWCE1CK</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CP2609140012</t>
+          <t>CP2609160013 DC2608280030</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>310</v>
+        <v>2737</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:10</t>
+          <t>2026-09-29 14:59:46</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP2-001612</t>
+          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>310</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2609141P4RQJXW</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>310</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-09-14 14:57:10</t>
-        </is>
+        <v>9036</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP2-001613</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>311</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>2609141P4RQJXW</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>311</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-09-14 14:57:10</t>
-        </is>
+        <v>1820</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>390</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2609141KA8DDEA</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>390</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-09-14 15:05:24</t>
+        <v>141</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP2-001755</t>
+          <t>SP2-001869+SP2-001870</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>594</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2609141KA8DDEA</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>CP2609140012</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>594</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-09-14 15:05:24</t>
-        </is>
+        <v>903</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MNL-002435</t>
+          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2737</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2609251AWCE1CK</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>CP2609160013 DC2608280030</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>2737</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:59:46</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>OC</t>
-        </is>
+        <v>1241</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SP1-001567+SP1-001568+SP1-001569+SP1-001570</t>
+          <t>SP2-001858+SP2-001859</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9036</v>
+        <v>1861</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DC2608310029 DC2609140003</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1820</v>
+        <v>832</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>141</v>
+        <v>794</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>PR5-000661</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>903</v>
+        <v>8602</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SP2-001749+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1241</v>
+        <v>11997</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SP2-001858+SP2-001859</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1861</v>
+        <v>2931</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>46279</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46295</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>DC2608310029 DC2609140003</t>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46304.99998842592</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>832</v>
+        <v>1234</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -2140,7 +2193,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q47" s="3" t="n">
@@ -2151,22 +2204,22 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 832</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>794</v>
+        <v>950</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -2177,7 +2230,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q48" s="3" t="n">
@@ -2188,59 +2241,82 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 794</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PR5-000661</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8602</v>
+        <v>1017</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>260930DC4DT2CY</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1017</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:00:19</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 8602</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SP1-001445+SP1-001446+SP1-001447+SP1-001448</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>11997</v>
+        <v>955</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -2249,9 +2325,32 @@
       <c r="E50" s="3" t="n">
         <v>46304.99998842592</v>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>260930DWC0FFR9</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CP2609220002</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>955</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:18:21</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q50" s="3" t="n">
@@ -2262,22 +2361,22 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 11997</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2931</v>
+        <v>1449</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -2286,9 +2385,32 @@
       <c r="E51" s="3" t="n">
         <v>46304.99998842592</v>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2609287HFYKV3U</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CP2609220007</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>1449</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:52:56</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609220007</t>
         </is>
       </c>
       <c r="Q51" s="3" t="n">
@@ -2299,120 +2421,166 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 2931</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1234</v>
+        <v>1566</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46304</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2609288A3EJJGE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1566</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:15:10</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="R52" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46304</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1234</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 1566</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP1-001210</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>950</v>
+        <v>1412</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46304</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>260929AW9BRK4J</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DC2609220002</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1412</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:15:43</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>DC2609220002</t>
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46288</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46304</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 950</t>
+          <t>Shp/TT เดือน ก.ย. ราคา 1412</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP4-000241</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1017</v>
+        <v>400</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2608280023</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46031</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46275</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>260930DC4DT2CY</t>
+          <t>260929BD1UJHCV</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2608280023</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1017</v>
+        <v>400</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-02 16:00:19</t>
+          <t>2026-10-02 16:35:35</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -2422,93 +2590,61 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>DC2608280023</t>
         </is>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46031</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46275</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1017</t>
+          <t>Shp Lzd TT ราคา400</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP4-000076</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>955</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>640</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>260930DWC0FFR9</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
+          <t>2610071JEP9U3K</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>955</v>
+        <v>590</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-02 16:18:21</t>
+          <t>2026-10-08 10:54:25</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>CP2609220002</t>
-        </is>
-      </c>
-      <c r="Q55" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R55" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 955</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1449</v>
+        <v>9551</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -2519,20 +2655,20 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2609287HFYKV3U</t>
+          <t>260930D84RADEG</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1449</v>
+        <v>9551</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-02 15:52:56</t>
+          <t>2026-10-02 16:17:19</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -2542,7 +2678,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>CP2609220007</t>
+          <t>CP2609220002</t>
         </is>
       </c>
       <c r="Q56" s="3" t="n">
@@ -2553,46 +2689,46 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1449</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SP1-001113</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1566</v>
+        <v>1199</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>DC2609220006</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2609288A3EJJGE</t>
+          <t>260930DWC0FFR9</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>DC2609220006</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1566</v>
+        <v>1199</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-02 16:15:10</t>
+          <t>2026-10-02 16:18:21</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -2602,100 +2738,62 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>DC2609220006</t>
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>46288</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>46304</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 1566</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SP1-001210</t>
+          <t>MS2-000754</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1412</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>46304</v>
+        <v>375</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>260929AW9BRK4J</t>
+          <t>260929BD1UJHCV</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>DC2609220002</t>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1412</v>
+        <v>375</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-02 16:15:43</t>
+          <t>2026-10-02 16:35:35</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>DC2609220002</t>
-        </is>
-      </c>
-      <c r="Q58" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="R58" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคา 1412</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SP4-000241</t>
+          <t>MS2-000820</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>400</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>DC2608280023</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>46031</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>46275</v>
+        <v>225</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -2704,11 +2802,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>DC2608280023</t>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>400</v>
+        <v>225</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -2717,51 +2815,40 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>DC2608280023</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>46031</v>
-      </c>
-      <c r="R59" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Shp Lzd TT ราคา400</t>
+          <t>MANUAL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SP4-000076</t>
+          <t>MS2-000942</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2610071JEP9U3K</t>
+          <t>260929BD1UJHCV</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>590</v>
+        <v>450</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-08 10:54:25</t>
+          <t>2026-10-02 16:35:35</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>MANUAL</t>
         </is>
       </c>
     </row>
@@ -2772,35 +2859,35 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9551</v>
+        <v>9673</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46274.00001157408</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46303.99998842592</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>260930D84RADEG</t>
+          <t>261001FNX3QHKT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>9551</v>
+        <v>9673</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-02 16:17:19</t>
+          <t>2026-10-02 17:47:09</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -2810,216 +2897,270 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CP2609220002</t>
+          <t>CP2609090005</t>
         </is>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>46288.00001157408</v>
+        <v>46274.00001157408</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>46303.99998842592</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซท 9551</t>
+          <t>Dynamic ก.ย. Shp ราคา 9673</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>MNL-002445</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1199</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46304.99998842592</v>
+        <v>2847</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>260930DWC0FFR9</t>
+          <t>261001FVHQUH0S</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>DC2609220006</t>
+          <t>CP2609280021 DC2609280008</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>1199</v>
+        <v>2847</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-02 16:18:21</t>
+          <t>2026-10-02 16:32:59</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>DC2609220006</t>
-        </is>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>46288.00001157408</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>46304.99998842592</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
+          <t>OC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MS2-000754</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>375</v>
+        <v>1603</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>261002HSH1MCYP</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>375</v>
+        <v>1603</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-02 18:00:21</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MS2-000820</t>
+          <t>SP1-001449</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>225</v>
+        <v>2220</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E64" t="n">
+        <v>46336</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>2610071VPKHFM4</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>225</v>
+        <v>2220</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-08 11:50:32</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46336</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 2220</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MS2-000942</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>450</v>
+        <v>851</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>46296.0000115741</v>
+      </c>
+      <c r="E65" t="n">
+        <v>46326.9999884259</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>260929BD1UJHCV</t>
+          <t>26100839JAVCJ8</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>450</v>
+        <v>851</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-02 16:35:35</t>
+          <t>2026-10-08 11:26:00</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SP1-001420+SP1-001421+SP1-001422+SP1-001423</t>
+          <t>SP2-001607+SP2-001754</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>9673</v>
+        <v>810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>46274.00001157408</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>46303.99998842592</v>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>46296.0000115741</v>
+      </c>
+      <c r="E66" t="n">
+        <v>46326.9999884259</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>261001FNX3QHKT</t>
+          <t>2610072GWE2YKY</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>9673</v>
+        <v>810</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-02 17:47:09</t>
+          <t>2026-10-08 11:19:24</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -3029,319 +3170,583 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CP2609090005</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>46274.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Dynamic ก.ย. Shp ราคา 9673</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MNL-002445</t>
+          <t>MS2-000818</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2847</v>
+        <v>225</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>261001FVHQUH0S</t>
+          <t>261007288HJTKT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>CP2609290069 DC2609290002</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>2847</v>
+        <v>225</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-02 16:32:59</t>
+          <t>2026-10-08 11:12:30</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SP1-001113</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>46032</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>261002HSH1MCYP</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>1603</v>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>07/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-02 18:00:21</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-08 11:16:15</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="n">
-        <v>46032</v>
-      </c>
-      <c r="R68" s="3" t="n">
-        <v>46326</v>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>07/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>20/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
+          <t>FS Shp ราคาเซ็ทละ 1052</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SP1-001449</t>
+          <t>SP2-001803+SP2-001804+SP2-001805+SP2-001806</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2220</v>
+        <v>2993</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2610071NYB574H</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>2993</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-08 11:05:23</t>
+          <t>2026-10-08 11:46:06</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R69" s="3" t="n">
-        <v>46336</v>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Shp+Lzd+Tiktok ราคา 2220</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2993</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SP2-001778+SP2-001779</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>851</v>
+        <v>1227</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-08 11:09:24</t>
+          <t>2026-10-08 11:21:10</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q70" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R70" s="3" t="n">
-        <v>46326.99998842592</v>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>01/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>31/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1227</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SP2-001607+SP2-001754</t>
+          <t>SP1-001378</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>810</v>
+        <v>3042</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CP2610020012</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>11/11/2026</t>
+        </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-08 11:10:32</t>
+          <t>2026-10-08 11:25:03</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
-        </is>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>46326.99998842592</v>
+          <t>CP2610020012</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>11/11/2026</t>
+        </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 810</t>
+          <t>Dynamic ต.ค. Shp ราคา 3042</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MS2-000818</t>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>225</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>261007288HJTKT</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>CP2609290069 DC2609290002</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>225</v>
+        <v>1849</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CP2609210010</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>21/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-08 11:12:30</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-08 11:37:15</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>CP2609210010</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>21/09/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>08/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Dynamic ก.ย. Shp ราคาเซท 1849</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>993</v>
+        <v>952</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>46152.00001157408</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>46315.99998842592</v>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>07/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20/10/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>26100718VN19D3</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>952</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-08 11:13:20</t>
+          <t>2026-10-08 11:40:06</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
-        </is>
-      </c>
-      <c r="Q73" s="3" t="n">
-        <v>46152.00001157408</v>
-      </c>
-      <c r="R73" s="3" t="n">
-        <v>46315.99998842592</v>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>07/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>20/10/2026 23:59:59</t>
+        </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+          <t>FS Shp ราคาเซท 952</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1052</v>
+        <v>993</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>05/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>11/11/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>5 4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>261003K6J8B8H5</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>CP2609140012</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>993</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-08 11:16:15</t>
+          <t>2026-10-08 11:49:26</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>CP + OC</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>CP2610060010</t>
+          <t>CP2610050027</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>07/10/2026 00:00:01</t>
+          <t>05/10/2026 00:00:01</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>20/10/2026 23:59:59</t>
+          <t>11/11/2026 23:59:59</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>FS Shp ราคาเซ็ทละ 1052</t>
+          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SP2-001753+SP2-001755</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>993</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>05/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>11/11/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:49:26</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>05/10/2026 00:00:01</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>11/11/2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SP4-000302</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>139</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>261005SRV913UJ</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>139</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:52:06</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S74"/>
+  <autoFilter ref="A1:S76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -537,81 +537,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>PR2-000471</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1056</v>
+        <v>2274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46337</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>261006TSHP0SJ6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CP2610020012</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2274</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:09</t>
+          <t>2026-10-09 15:47:26</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1056</t>
+          <t>Dynamic ต.ค. Shp ราคา 2274</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>PR3-000099</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139</v>
+        <v>10238</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CP2609040005</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>261007247UHVK3</t>
+          <t>2610095VAKA4EC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CP2609040005</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>139</v>
+        <v>10238</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:52:16</t>
+          <t>2026-10-09 15:32:16</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,33 +639,33 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CP2609040005</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>46269</v>
+        <v>46304</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>46303</v>
+        <v>46326</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Shp Fs ถูกชัวร์ ราคา139</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 10238</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>PR5-000503</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>2128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -656,14 +674,32 @@
       <c r="E4" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>261006W04KNW1R</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2128</v>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:52:05</t>
+          <t>2026-10-09 16:20:47</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q4" s="3" t="n">
@@ -674,79 +710,106 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 2128</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PR3-000099</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10430</v>
+        <v>2503</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>261005TDQDY6TH</t>
+          <t>2610083S15MCPJ</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CP2609300041</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>10430</v>
+        <v>2503</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:57</t>
+          <t>2026-10-09 16:50:46</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>CP</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 2503</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>PR5-000635</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>969</v>
+        <v>8671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>261007288HJTKT</t>
+          <t>261006VFPUVVQ5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>969</v>
+        <v>8671</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-08 17:53:17</t>
+          <t>2026-10-09 16:17:20</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -756,201 +819,251 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>Dynamic ต.ค. Shp ราคา 8671</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP4-000241</t>
+          <t>PR5-000667</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>7212</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46336</v>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>26100725KET83K</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7212</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-08 17:19:27</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>DC2610010003</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Shp+Lzd+Tiktok ราคา 405</t>
+          <t>2026-10-09 16:38:23</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>PR5-000673</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1330</v>
+        <v>8058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>261006VGXVPTEY</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>8058</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-08 17:20:12</t>
+          <t>2026-10-09 15:56:12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 8058</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>PR5-000677</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1849</v>
+        <v>4530</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CP2609210010</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46286.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46326</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2610083XE0YD4V</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>4530</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-08 17:20:57</t>
+          <t>2026-10-09 16:54:12</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CP2609210010</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>46286.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Dynamic ก.ย. Shp ราคาเซท 1849</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 4530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>PR5-000683</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>952</v>
+        <v>1755</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CP2610060006</t>
+          <t>DC2610020003</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46302.00001157408</v>
+        <v>46297</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46315.99998842592</v>
+        <v>46337</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2610082P9HJV99</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DC2610020003</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1755</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-08 17:25:46</t>
+          <t>2026-10-09 16:45:56</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CP2610060006</t>
+          <t>DC2610020003</t>
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>46302.00001157408</v>
+        <v>46297</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>46315.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>FS Shp ราคาเซท 952</t>
+          <t>Dynamic ต.ค. Shp ราคา 1755</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SP4-000196</t>
+          <t>PR5-000683</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>305</v>
+        <v>1669</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2609300021</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -959,14 +1072,32 @@
       <c r="E11" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2610071JD7K8N4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1669</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-08 17:22:44</t>
+          <t>2026-10-09 16:30:18</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>DC2609300021</t>
         </is>
       </c>
       <c r="Q11" s="3" t="n">
@@ -977,88 +1108,84 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 1669</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>PR5-000686</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1477</v>
+        <v>4983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46326.99998842592</v>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>261006V0Y0CJCQ</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>4983</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23:30</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CP2609300040</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>46296.00001157408</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>46326.99998842592</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>2026-10-09 15:52:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>PR6-000223</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>993</v>
+        <v>4537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46300.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46337.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2610071U7NJ4MH</t>
+          <t>261006UJQVTNTJ</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>993</v>
+        <v>4537</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-08 17:46:50</t>
+          <t>2026-10-09 16:14:45</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1068,57 +1195,57 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>CP2610020012</t>
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>46300.00001157408</v>
+        <v>46063</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>46337.99998842592</v>
+        <v>46337</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+          <t>Dynamic ต.ค. Shp ราคา 4537</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP1-001113</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1280</v>
+        <v>1603</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2610071YKH3P16</t>
+          <t>2610084KU6WNU4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1280</v>
+        <v>1603</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-08 17:50:28</t>
+          <t>2026-10-09 12:01:30</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1128,57 +1255,57 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001414+SP2-001415+SP2-001416+SP2-001417</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>974</v>
+        <v>1128</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26100729ENA013</t>
+          <t>26100963TRWGR3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>974</v>
+        <v>1128</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-08 17:55:09</t>
+          <t>2026-10-09 15:41:03</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1188,197 +1315,367 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>CP2610070014</t>
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1128</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SP4-000076</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>590</v>
+        <v>1280</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2610071JEP9U3J</t>
+          <t>26100845P38NYB</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>590</v>
+        <v>1280</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-08 17:36:01</t>
+          <t>2026-10-09 11:50:22</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SP2-001869+SP2-001870</t>
+          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>921</v>
+        <v>1253</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26100956M2WE0Q</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1253</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-08 17:47:27</t>
+          <t>2026-10-09 12:07:21</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DC2609290041</t>
+          <t>CP2610070011</t>
         </is>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 921</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1253</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SP1-001449</t>
+          <t>SP2-001678+SP2-001679+SP2-001680+SP2-001681</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2220</v>
+        <v>2974</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>261008513P2D80</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2974</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-08 17:47:58</t>
+          <t>2026-10-09 12:06:25</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>46296</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>46336</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Shp+Lzd+Tiktok ราคา 2220</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MS2-000818</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>225</v>
+        <v>952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
-        </is>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>46302.00001157408</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46315.99998842592</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>261007288HJTKT</t>
+          <t>26100718VN19D3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>CP2610060006</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>225</v>
+        <v>952</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-08 17:53:17</t>
+          <t>2026-10-09 11:43:38</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>CP</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>46302.00001157408</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
+          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1052</v>
+        <v>974</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2610084C4VS82X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>974</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54:11</t>
+          <t>2026-10-09 11:58:42</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CP2610060010</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>46302.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>46315.99998842592</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>FS Shp ราคาเซ็ทละ 1052</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1056</v>
+        <v>1227</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>261008494XV9ND</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1227</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:09</t>
+          <t>2026-10-09 11:54:31</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="Q21" s="3" t="n">
@@ -1389,269 +1686,458 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1056</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PR3-000099</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10430</v>
+        <v>1052</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CP2609300041</t>
-        </is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>46302.00001157408</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46315.99998842592</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>261005TDQDY6TH</t>
+          <t>2610084TS30HKC</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CP2609300041</t>
+          <t>CP2610060010</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>10430</v>
+        <v>1052</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-08 17:16:57</t>
+          <t>2026-10-09 12:04:55</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>CP</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>46302.00001157408</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซ็ทละ 1052</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>969</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>261007288HJTKT</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>CP2609290081</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>969</v>
+        <v>1199</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DC2609220006</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>46288.00001157408</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46304.99998842592</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-08 17:53:17</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-09 12:12:08</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CP2609290081</t>
+          <t>DC2609220006</t>
         </is>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46288.00001157408</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46304.99998842592</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
+          <t>Shp/TT เดือน ก.ย. ราคาเซ็ทละ 1199</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SP4-000241</t>
+          <t>SP2-001713+SP2-001714+SP2-001715+SP2-001716</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>405</v>
+        <v>1199</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>26100956TPKHNE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1199</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-08 17:19:27</t>
+          <t>2026-10-09 12:12:20</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DC2610010003</t>
+          <t>DC2610070012</t>
         </is>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>46032</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>46336</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Shp+Lzd+Tiktok ราคา 405</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1199</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SP2-001748+SP2-001615+SP2-001616+SP2-001617</t>
+          <t>SP2-001717</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1330</v>
+        <v>425</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2610084EQCG957</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>425</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-08 17:20:12</t>
+          <t>2026-10-09 12:00:48</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DC2609290042</t>
+          <t>DC2610010003</t>
         </is>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46306</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 1330</t>
+          <t>Shp+Lzd+Tiktok ราคา 425</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1849</v>
+        <v>1056</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2610084BHD35QS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1056</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-08 17:20:57</t>
+          <t>2026-10-09 11:56:02</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CP2609210010</t>
+          <t>CP2609300040</t>
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>46286.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>46303.99998842592</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Dynamic ก.ย. Shp ราคาเซท 1849</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1056</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>952</v>
+        <v>993</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>46300.00001157408</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46337.99998842592</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2610071CNVJU2Q</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CP2610050027</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>993</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-08 17:25:46</t>
+          <t>2026-10-09 11:46:05</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CP2610060006</t>
+          <t>CP2610050027</t>
         </is>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>46302.00001157408</v>
+        <v>46300.00001157408</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>46315.99998842592</v>
+        <v>46337.99998842592</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>FS Shp ราคาเซท 952</t>
+          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SP4-000196</t>
+          <t>SP2-001753+SP2-001755</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>305</v>
+        <v>1034</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2610095H5YJYG4</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1034</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-08 17:22:44</t>
+          <t>2026-10-09 12:08:09</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DC2609300024</t>
+          <t>CP2610070011</t>
         </is>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>46296</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1034</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
+          <t>SP2-001778+SP2-001779</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1477</v>
+        <v>851</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2610084S0WAP2B</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DC2609290041</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>851</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23:30</t>
+          <t>2026-10-09 12:04:03</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>CP</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CP2609300040</t>
+          <t>DC2609290041</t>
         </is>
       </c>
       <c r="Q29" s="3" t="n">
@@ -1662,22 +2148,33 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 851</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SP2-001610+SP2-001611+SP2-001612+SP2-001613</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1280</v>
+        <v>1477</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2610071YKH3P16</t>
+          <t>2610084EQCG957</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1686,11 +2183,11 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1280</v>
+        <v>1477</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-08 17:50:28</t>
+          <t>2026-10-09 12:00:48</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -1711,35 +2208,46 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1280</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซ็ทละ 1477</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SP2-001753+SP2-001755</t>
+          <t>SP2-001799+SP2-001800+SP2-001801+SP2-001802</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>993</v>
+        <v>1889</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2610071U7NJ4MH</t>
+          <t>261008513P2D80</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>993</v>
+        <v>1889</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-08 17:46:50</t>
+          <t>2026-10-09 12:06:25</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -1749,33 +2257,44 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CP2610050027</t>
+          <t>CP2609290081</t>
         </is>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>46152.00001157408</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>46337.99998842592</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>FS Shp ถูกชัวร์ ราคาเซ็ทละ 993</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 1889</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SP2-001703+SP2-001596+SP2-001597+SP2-001598</t>
+          <t>SP2-001845+SP2-001846+SP2-001847+SP2-001848</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>974</v>
+        <v>969</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46326.99998842592</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26100729ENA013</t>
+          <t>2610084AXQ548E</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1784,11 +2303,11 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-08 17:55:09</t>
+          <t>2026-10-09 11:55:21</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -1809,35 +2328,46 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Shp/TT เดือน ต.ค. ราคาเซท 974</t>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 969</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MS2-000818</t>
+          <t>SP4-000196</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>225</v>
+        <v>305</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>261007288HJTKT</t>
+          <t>26100717549GJX</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CP2609290069 DC2609290002</t>
+          <t>DC2609300024</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-08 17:53:17</t>
+          <t>2026-10-09 11:41:05</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -1845,9 +2375,1262 @@
           <t>CP</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 305</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SP4-000241</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>405</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2610084DVJ6W6W</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>405</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:59:14</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DC2610010003</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Shp+Lzd+Tiktok ราคา 405</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SP4-000302</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>139</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2610084NP759P9</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>139</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:03:21</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DC2609300024</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 139</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SP4-000302</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>142</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2610095VAKA4EC</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>142</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:32:16</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 142</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8618</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:18:47</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 8618</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PR6-000277</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5304</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>261006VR7E6YBP</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>5304</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:32:38</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 5304</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PR6-000223</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4410</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2610083V0VVBCD</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>4410</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:55:16</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4410</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PR5-000631</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1669</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2610083WPS4THV</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1669</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:55:52</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1669</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PR6-000170</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6306</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2610071832RHFY</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>6306</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:34:39</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 6306</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6055</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2610071BYJ7X5E</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>6055</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:38:31</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 6055</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PR5-000645</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3997</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CP2610060009</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2610071AA2DK93</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CP2610060009</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>3997</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:36:32</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CP2610060009</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>FS Shp ราคา 3997</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PR1-000584</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1252</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2610083PXSTGXP</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>1252</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:54:34</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DC2609300021</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2610071H7M1J0B</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>2165</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:41:28</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PR5-000681</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2659</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DC2610020005</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46337</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2610071KCY80UD</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DC2610020005</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>2659</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:42:05</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DC2610020005</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46337</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 2659</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PR6-000446</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6270</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>26100721GYMAWW</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>6270</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:45:42</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 6270</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4625</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>26100729Q35MAX</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>4625</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:48:46</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4625</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PR6-000445</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5507</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>261007252AEWRW</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>5507</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:46:57</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CP2609290084</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 5507</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>15615</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2610083XRBVTMU</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>15615</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:56:35</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CP2609290081</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 15615</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PR5-000667</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6383</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2610082JXTGRUJ</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>6383</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:50:36</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CP2610060010</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>FS Shp ราคา 6383</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PR2-000495</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4565</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2610082K71NDWN</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>4565</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:51:13</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4565</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3183</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2610083MKMP7HY</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>3183</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:53:52</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>CP2609300040</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 3183</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>10430</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2610083WD60HJX</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>10430</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:52:49</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46326</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S33"/>
+  <autoFilter ref="A1:S54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3629,8 +3629,1164 @@
         <v>46326</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MNL-002120</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7225</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CP2609300027</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>261003K7HY2GGE</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CP2609300027</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>7225</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:42:45</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CP2609300027</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>promotion xmn viewsonic period 1-31 oct 2026  topup all store (viewsonic sup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MNL-002445</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2847</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>261006UWKM892H</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>2847</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:07:55</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MNL-002423</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>15857</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:26:27</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MNL-002416</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2829</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:27:05</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 1 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MNL-002550</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2977</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:27:38</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MNL-002358</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2157</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:29:03</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MNL-002403</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>6372</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="M61" t="n">
+        <v>6505</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:22:50</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3724</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:46:54</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MNL-002404</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>6792</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>26100714TQ0CEY</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>6792</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:22:39</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MNL-002507</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2187</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:23:11</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MNL-002584</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2610071822BPS6</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-10-10 11:41:31</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MNL-002489</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2869</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:24:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MNL-002505</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>7461</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2610071AX38J9S</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>7461</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:51:06</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MNL-002555</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3460</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:25:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MNL-002478</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3133</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:25:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MNL-002483</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3405</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:26:27</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>CP2610050031</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 05-11 oct 26 addon online (bg260024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MNL-002409</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2922</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2610107P8TY5NB</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>2922</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:51:29</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3601</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:31:59</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3691</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2610107P9GX020</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>3691</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:47:45</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn lenovo period 1-30 oct 2026 topup all store bg260044, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MNL-002498</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3548</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2610107P9E19NE</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>3548</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:48:44</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MNL-002483</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3476</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2610107PFGN2MY</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>3476</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:49:23</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MNL-002484</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46301.00001157408</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>26100979W27913</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>4648</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:50:22</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>46301.00001157408</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Promotion xmn lg period 06-31 oct 2026 topup all store bg250024</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MNL-002505</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7617</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2610096GCN7NY6</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>7617</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:51:26</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MNL-002403</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>6505</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2610107P9A8HRX</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>6505</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:22:46</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MNL-002371</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>8351</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2610096EP9QSXE</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>8351</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:22:48</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MNL-002437</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>5619</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:54:17</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MNL-002409</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2863</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CP2610100002 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2610107PUSHD2B</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>CP2610100002 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>2863</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:52:49</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>CP2610100002 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S54"/>
+  <autoFilter ref="A1:S81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3899,15 +3899,38 @@
       <c r="B62" t="n">
         <v>3724</v>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
       <c r="D62" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2610108S3ECHP2</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>3801</v>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-10 16:46:54</t>
+          <t>2026-10-11 14:47:22</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4098,7 +4121,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2610071AX38J9S</t>
+          <t>2610107STQYFGF</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4111,12 +4134,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-10 16:51:06</t>
+          <t>2026-10-11 11:47:42</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>AUTO_MATCH</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -4175,9 +4198,15 @@
       <c r="B70" t="n">
         <v>3405</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46306</v>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-10 10:26:27</t>
+          <t>2026-10-11 11:22:02</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -4219,7 +4248,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2610107P8TY5NB</t>
+          <t>2610108SJ1PRV7</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4232,12 +4261,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-10 17:51:29</t>
+          <t>2026-10-11 10:17:47</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -4260,119 +4289,159 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3601</v>
+        <v>3691</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2610097EXDCKQJ</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>3691</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-10 17:31:59</t>
-        </is>
+          <t>2026-10-11 15:08:12</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+          <t>promotion xdt xmn lenovo period 1-30 oct 2026 topup all store bg260044, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-002483</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3691</v>
+        <v>3476</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2610107P9GX020</t>
+          <t>2610107S36HV0X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>3691</v>
+        <v>3476</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-10 16:47:45</t>
+          <t>2026-10-11 16:09:36</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>AUTO_MATCH</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>promotion xdt xmn lenovo period 1-30 oct 2026 topup all store bg260044, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MNL-002498</t>
+          <t>MNL-002505</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3548</v>
+        <v>7617</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2610107P9E19NE</t>
+          <t>2610107PQXJ4XH</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>3548</v>
+        <v>7617</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-10 16:48:44</t>
+          <t>2026-10-11 17:32:42</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -4382,29 +4451,29 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MNL-002483</t>
+          <t>MNL-002403</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3476</v>
+        <v>6505</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4419,7 +4488,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2610107PFGN2MY</t>
+          <t>2610097DGHNNQD</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4428,16 +4497,16 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>3476</v>
+        <v>6505</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-10 16:49:23</t>
+          <t>2026-10-11 11:57:09</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>AUTO_MATCH</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -4460,71 +4529,71 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MNL-002484</t>
+          <t>MNL-002371</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4648</v>
+        <v>8351</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CP2610060002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>46301.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>26100979W27913</t>
+          <t>2610108NSJYSG5</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CP2610060002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>4648</v>
+        <v>8351</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-10 16:50:22</t>
+          <t>2026-10-11 12:07:07</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CP2610060002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>46301.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>46326.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Promotion xmn lg period 06-31 oct 2026 topup all store bg250024</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MNL-002505</t>
+          <t>MNL-002437</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>7617</v>
+        <v>5636</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4539,7 +4608,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2610096GCN7NY6</t>
+          <t>2610107SB71MWN</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4548,16 +4617,16 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>7617</v>
+        <v>5636</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-10 16:51:26</t>
+          <t>2026-10-11 17:18:30</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -4580,15 +4649,15 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MNL-002403</t>
+          <t>MNL-002409</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6505</v>
+        <v>2863</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -4599,30 +4668,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2610107P9A8HRX</t>
+          <t>2610108EP7CMBA</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>6505</v>
+        <v>2863</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-10 17:22:46</t>
+          <t>2026-10-11 10:23:01</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>AUTO_MATCH</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="Q78" s="3" t="n">
@@ -4633,22 +4702,22 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MNL-002371</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8351</v>
+        <v>3601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
@@ -4657,39 +4726,21 @@
       <c r="E79" s="3" t="n">
         <v>46326</v>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2610096EP9QSXE</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>8351</v>
-      </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-10 17:22:48</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>AUTO_MATCH</t>
+          <t>2026-10-11 14:51:05</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
         </is>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>46296</v>
+        <v>46306</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>46326</v>
+        <v>46308</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -4700,93 +4751,834 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MNL-002437</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5619</v>
+        <v>3801</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2610108XBAEBKT</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>3801</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-10 16:54:17</t>
-        </is>
+          <t>2026-10-11 14:47:22</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MNL-002409</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2863</v>
+        <v>3491</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:54:07</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3591</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:08:02</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MNL-002498</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3475</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2610108TG32DDA</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>3475</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:05:34</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MNL-002498</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3548</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="G84" t="n">
+        <v>73</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2610107SFJB70Y</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>3548</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:58:43</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MNL-002435</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2782</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2610107R3QEQNB</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>2782</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2026-10-11 11:09:40</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>CP2609280021 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MNL-002437</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5619</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>31/10/2026</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2610107PUSHD2B</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="G86" t="n">
+        <v>11</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2610107PGB9Q6F</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
-      <c r="M81" t="n">
-        <v>2863</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>2026-10-10 17:52:49</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
+      <c r="M86" t="n">
+        <v>5619</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:52:41</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>CP + OC</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MNL-002412</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2781</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100002</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2610107PGB9Q6F</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>CP2610100002 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>2781</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:52:41</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
         <is>
           <t>CP</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>CP2610100002 DC2609280008</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>31/10/2026</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3601</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2610097JD5824X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>3601</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:52:33</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3601</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2610097D96386F</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>3601</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:51:05</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3491</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:54:07</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3491</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2610097EKRWPYW</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>3491</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:58:04</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3591</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:53:51</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>coupon voucher</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MNL-002420</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3601</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:47:22</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MNL-002511</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3491</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:57:09</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>CP2610110001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MNL-002484</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>46301.00001157408</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="G95" t="n">
+        <v>62</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>26101082C317K0</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>4648</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:27:26</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="n">
+        <v>46301.00001157408</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Promotion xmn lg period 06-31 oct 2026 topup all store bg250024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S81"/>
+  <autoFilter ref="A1:S95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/cp_data.xlsx
+++ b/projects/auto_page/autopageMKII/tables/cp_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$S$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$V$257</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:V257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,21 @@
           <t>suggested_remark</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pattern_discount</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>couponDetailCash</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>couponDetailDisc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,7 +564,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>46337</v>
@@ -569,7 +584,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:47:26</t>
+          <t>2026-10-13 13:17:10</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -583,7 +598,7 @@
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>46337</v>
@@ -609,14 +624,14 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46304</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2610095VAKA4EC</t>
+          <t>261012DV332UFD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -629,7 +644,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-09 15:32:16</t>
+          <t>2026-10-13 13:23:36</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -643,15 +658,18 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>46304</v>
+        <v>46304.00001157408</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>Shp/TT เดือน ต.ค. ราคา 10238</t>
         </is>
+      </c>
+      <c r="T3" t="n">
+        <v>2062</v>
       </c>
     </row>
     <row r="4">
@@ -689,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-09 16:20:47</t>
+          <t>2026-10-13 13:04:22</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,7 +767,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-09 16:50:46</t>
+          <t>2026-10-13 13:01:24</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -789,7 +807,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>46337</v>
@@ -809,7 +827,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-09 16:17:20</t>
+          <t>2026-10-13 13:18:04</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -823,7 +841,7 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>46337</v>
@@ -848,6 +866,12 @@
           <t>CP2609300041</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46326</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>26100725KET83K</t>
@@ -863,12 +887,28 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-09 16:38:23</t>
+          <t>2026-10-13 13:29:16</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>AUTO_MATCH</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 7212</t>
         </is>
       </c>
     </row>
@@ -907,7 +947,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-09 15:56:12</t>
+          <t>2026-10-13 13:13:01</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -967,7 +1007,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-09 16:54:12</t>
+          <t>2026-10-13 13:10:54</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1027,7 +1067,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45:56</t>
+          <t>2026-10-13 13:02:22</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1087,7 +1127,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-09 16:30:18</t>
+          <t>2026-10-13 13:02:22</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1126,6 +1166,12 @@
           <t>CP2609300041</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46326</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>261006V0Y0CJCQ</t>
@@ -1141,12 +1187,28 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-09 15:52:00</t>
+          <t>2026-10-13 13:30:12</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>CP</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CP2609300041</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4983</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1227,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>46337</v>
@@ -1185,7 +1247,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-09 16:14:45</t>
+          <t>2026-10-13 13:15:21</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1199,7 +1261,7 @@
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>46337</v>
@@ -2594,7 +2656,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-09 16:18:47</t>
+          <t>2026-10-13 13:18:04</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -2649,7 +2711,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-09 17:32:38</t>
+          <t>2026-10-13 13:16:17</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2709,7 +2771,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-09 17:55:16</t>
+          <t>2026-10-13 13:15:21</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2769,7 +2831,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-09 17:55:52</t>
+          <t>2026-10-13 13:06:05</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2889,7 +2951,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-09 17:38:31</t>
+          <t>2026-10-13 13:14:44</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -2936,7 +2998,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2610071AA2DK93</t>
+          <t>261012E1UDHQQ5</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2949,7 +3011,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-09 17:36:32</t>
+          <t>2026-10-13 13:10:19</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3009,7 +3071,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-09 17:54:34</t>
+          <t>2026-10-13 13:00:24</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3069,7 +3131,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-09 17:41:28</t>
+          <t>2026-10-13 13:17:10</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3249,7 +3311,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-09 17:48:46</t>
+          <t>2026-10-13 13:19:39</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3369,7 +3431,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-09 17:56:35</t>
+          <t>2026-10-13 13:20:36</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3429,7 +3491,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-09 17:50:36</t>
+          <t>2026-10-13 13:29:16</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3489,7 +3551,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-09 17:51:13</t>
+          <t>2026-10-13 13:03:26</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3549,7 +3611,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-09 17:53:52</t>
+          <t>2026-10-13 13:07:00</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3609,7 +3671,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-09 16:52:49</t>
+          <t>2026-10-13 13:23:17</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3628,6 +3690,11 @@
       <c r="R54" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 10430</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3704,10 +3771,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46308</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3724,7 +3791,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-10 13:07:55</t>
+          <t>2026-10-13 12:28:00</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -3738,10 +3805,10 @@
         </is>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46308</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -3760,8 +3827,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-10 12:26:27</t>
-        </is>
+          <t>2026-10-13 12:45:30</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -3798,34 +3876,93 @@
       <c r="B59" t="n">
         <v>2977</v>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>261012DTG81X3K</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>3039</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-10 12:27:38</t>
-        </is>
+          <t>2026-10-13 13:31:54</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>CP2610010047</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46310</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MNL-002358</t>
+          <t>MNL-002403</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2157</v>
+        <v>6372</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="M60" t="n">
+        <v>6505</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:03</t>
+          <t>2026-10-10 17:22:50</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CP2609290086 CP2610090037</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q60" s="3" t="n">
@@ -3836,22 +3973,22 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MNL-002403</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6372</v>
+        <v>3724</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2609290086 DC2609280008</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -3860,17 +3997,27 @@
       <c r="E61" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2610108S3ECHP2</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
       <c r="M61" t="n">
-        <v>6505</v>
+        <v>3801</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-10 17:22:50</t>
+          <t>2026-10-13 12:38:17</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>AUTO_MATCH</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -3893,118 +4040,100 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002404</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3724</v>
+        <v>6792</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46326</v>
+          <t>DC2609280008</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2610108S3ECHP2</t>
+          <t>26100714TQ0CEY</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3801</v>
+        <v>6792</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-11 14:47:22</t>
+          <t>2026-10-10 10:22:39</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MNL-002404</t>
+          <t>MNL-002507</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6792</v>
+        <v>2187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>26100714TQ0CEY</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>6792</v>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-10 10:22:39</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>OC</t>
+          <t>2026-10-10 10:23:11</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MNL-002507</t>
+          <t>MNL-002584</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2187</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CP2610100002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -4013,14 +4142,32 @@
       <c r="E64" s="3" t="n">
         <v>46326</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2610071822BPS6</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>2023</v>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-10 10:23:11</t>
+          <t>2026-10-13 12:44:00</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AUTO_MATCH</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CP2610100002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q64" s="3" t="n">
@@ -4031,87 +4178,93 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MNL-002584</t>
+          <t>MNL-002489</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2610071822BPS6</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>2023</v>
+        <v>2869</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-10 11:41:31</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>AUTO_MATCH</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="Q65" s="3" t="n">
-        <v>46293</v>
+          <t>2026-10-10 10:24:18</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MNL-002489</t>
+          <t>MNL-002505</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2869</v>
+        <v>7461</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2610107P93KYR8</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>7461</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-10 10:24:18</t>
+          <t>2026-10-13 12:39:06</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MNL-002505</t>
+          <t>MNL-002555</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>7461</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
+        <v>3460</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>46296</v>
@@ -4119,32 +4272,14 @@
       <c r="E67" s="3" t="n">
         <v>46326</v>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2610107STQYFGF</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>7461</v>
-      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-11 11:47:42</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
+          <t>2026-10-13 12:46:10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2609290087</t>
         </is>
       </c>
       <c r="Q67" s="3" t="n">
@@ -4155,85 +4290,175 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MNL-002555</t>
+          <t>MNL-002483</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3460</v>
+        <v>3405</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>46306</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-10 10:25:18</t>
+          <t>2026-10-11 11:22:02</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>CP2610050031</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 05-11 oct 26 addon online (bg260024)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MNL-002478</t>
+          <t>MNL-002409</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3133</v>
+        <v>2922</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2610108SJ1PRV7</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>2922</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-10 10:25:55</t>
+          <t>2026-10-13 13:35:00</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MNL-002483</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3405</v>
+        <v>3691</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46306</v>
+        <v>46326</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2610107PK066EH</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>3691</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-11 11:22:02</t>
+          <t>2026-10-13 12:32:19</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>CP2610050031</t>
+          <t>CP2609290086 DC2609280008</t>
         </is>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>46306</v>
+        <v>46326</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>promotion xmn lg period 05-11 oct 26 addon online (bg260024)</t>
+          <t>promotion xdt xmn lenovo period 1-30 oct 2026 topup all store bg260044, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MNL-002409</t>
+          <t>MNL-002483</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2922</v>
+        <v>3476</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4248,7 +4473,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2610108SJ1PRV7</t>
+          <t>261011BBQ6W52G</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4257,11 +4482,11 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>2922</v>
+        <v>3476</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-11 10:17:47</t>
+          <t>2026-10-13 12:42:00</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -4289,71 +4514,71 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-002505</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3691</v>
+        <v>7617</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46308</v>
+        <v>46326</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2610097EXDCKQJ</t>
+          <t>261011BMR7K76X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3691</v>
+        <v>7617</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-11 15:08:12</t>
+          <t>2026-10-13 12:39:29</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>CP2609290086 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>46308</v>
+        <v>46326</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>promotion xdt xmn lenovo period 1-30 oct 2026 topup all store bg260044, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MNL-002483</t>
+          <t>MNL-002403</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3476</v>
+        <v>6505</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4368,7 +4593,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2610107S36HV0X</t>
+          <t>2610097DGHNNQD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4377,16 +4602,16 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>3476</v>
+        <v>6505</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-11 16:09:36</t>
+          <t>2026-10-11 11:57:09</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -4409,11 +4634,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MNL-002505</t>
+          <t>MNL-002371</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7617</v>
+        <v>8351</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4428,7 +4653,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2610107PQXJ4XH</t>
+          <t>2610108NSJYSG5</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4437,16 +4662,16 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>7617</v>
+        <v>8351</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-11 17:32:42</t>
+          <t>2026-10-11 12:07:07</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -4469,11 +4694,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MNL-002403</t>
+          <t>MNL-002437</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6505</v>
+        <v>5636</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4488,7 +4713,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2610097DGHNNQD</t>
+          <t>2610107SB71MWN</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4497,11 +4722,11 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>6505</v>
+        <v>5636</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-11 11:57:09</t>
+          <t>2026-10-11 17:18:30</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -4529,116 +4754,98 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MNL-002371</t>
+          <t>MNL-002409</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>8351</v>
+        <v>2863</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2610108NSJYSG5</t>
+          <t>261012EFM1JCTM</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>8351</v>
+        <v>2863</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-11 12:07:07</t>
+          <t>2026-10-13 13:35:20</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="Q76" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MNL-002437</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5636</v>
+        <v>3601</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>46296</v>
+        <v>46306</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2610107SB71MWN</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>5636</v>
+        <v>46308</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-11 17:18:30</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
+          <t>2026-10-13 12:38:17</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>DC2609280008 CP2609290086 CP2610110001</t>
         </is>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>46296</v>
+        <v>46306</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>46326</v>
+        <v>46308</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -4649,15 +4856,15 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MNL-002409</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2863</v>
+        <v>3801</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
+          <t>CP2609290086 DC2609280008</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -4668,30 +4875,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2610108EP7CMBA</t>
+          <t>261010A1NS8GSJ</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
+          <t>CP2609290086 DC2609280008</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2863</v>
+        <v>3801</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-11 10:23:01</t>
+          <t>2026-10-13 12:38:22</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q78" s="3" t="n">
@@ -4702,18 +4909,18 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3601</v>
+        <v>3491</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4721,14 +4928,14 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>46296</v>
+        <v>46306</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46326</v>
+        <v>46308</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-11 14:51:05</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -4751,16 +4958,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3801</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CP2609290086 DC2609280008</t>
-        </is>
+        <v>3591</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>46296</v>
@@ -4768,32 +4970,14 @@
       <c r="E80" s="3" t="n">
         <v>46326</v>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2610108XBAEBKT</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>CP2609290086 DC2609280008</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>3801</v>
-      </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-11 14:47:22</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2609290086</t>
         </is>
       </c>
       <c r="Q80" s="3" t="n">
@@ -4804,336 +4988,369 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-002498</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3491</v>
+        <v>3475</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2609290086 CP2610110001</t>
+          <t>CP2609280028 DC2609280008</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46326</v>
+        <v>46308</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2610108TG32DDA</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>3475</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-11 14:54:07</t>
+          <t>2026-10-13 12:28:42</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2609290086 CP2610110001</t>
+          <t>CP2609280028 DC2609280008</t>
         </is>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>46308</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-002498</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3591</v>
+        <v>3548</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>46296</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46326</v>
+        <v>46308.99998842592</v>
+      </c>
+      <c r="G82" t="n">
+        <v>73</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>261011BHA4Q064</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>CP2609280028 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>3548</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-11 15:08:02</t>
+          <t>2026-10-13 12:29:05</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>OC</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>CP2609290086</t>
+          <t>CP2609280028 DC2609280008</t>
         </is>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>46296</v>
+        <v>46296.00001157408</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>46326</v>
+        <v>46308.99998842592</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MNL-002498</t>
+          <t>MNL-002435</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3475</v>
+        <v>2782</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>CP2609280021 DC2609280008</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46308</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2610108TG32DDA</t>
+          <t>2610107R3QEQNB</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>CP2609280021 DC2609280008</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>3475</v>
+        <v>2782</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-11 16:05:34</t>
+          <t>2026-10-13 12:30:52</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>CP2609280021 DC2609280008</t>
         </is>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46308</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MNL-002498</t>
+          <t>MNL-002437</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3548</v>
+        <v>5619</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="G84" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2610107SFJB70Y</t>
+          <t>2610107PGB9Q6F</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>3548</v>
+        <v>5619</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-11 10:58:43</t>
+          <t>2026-10-11 17:52:41</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP + OC</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>CP2609280028 DC2609280008</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MNL-002435</t>
+          <t>MNL-002412</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>DC2609280008 CP2610100002</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2610107R3QEQNB</t>
+          <t>2610107PGB9Q6F</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>CP2610100002 DC2609280008</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-11 11:09:40</t>
+          <t>2026-10-13 13:42:40</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>CP2609280021 DC2609280008</t>
+          <t>DC2609280008 CP2610100002</t>
         </is>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>46296.00001157408</v>
+        <v>46296</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>46308.99998842592</v>
+        <v>46326</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MNL-002437</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5619</v>
+        <v>3601</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>11</v>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2610107PGB9Q6F</t>
+          <t>2610097JD5824X</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>5619</v>
+        <v>3601</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-11 17:52:41</t>
+          <t>2026-10-13 12:38:17</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>CP + OC</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
+          <t>CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -5144,43 +5361,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MNL-002412</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2781</v>
+        <v>3601</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2610100002</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2610107PGB9Q6F</t>
+          <t>2610097D96386F</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CP2610100002 DC2609280008</t>
+          <t>CP2609290086 CP2610110001 DC2609280008</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2781</v>
+        <v>3601</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-11 17:52:41</t>
+          <t>2026-10-13 12:38:17</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -5190,78 +5403,45 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2610100002</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
+          <t>DC2609280008 CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3601</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>CP2609290086 CP2610110001 DC2609280008</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>46306</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2610097JD5824X</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>CP2609290086 CP2610110001 DC2609280008</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>3601</v>
+        <v>3491</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-11 14:52:33</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>CP2610110001</t>
+          <t>DC2609280008 CP2609290086</t>
         </is>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>46308</v>
+        <v>46326</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -5272,11 +5452,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002511</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3601</v>
+        <v>3491</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5291,7 +5471,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2610097D96386F</t>
+          <t>2610097EKRWPYW</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5300,11 +5480,11 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>3601</v>
+        <v>3491</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-11 14:51:05</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -5314,7 +5494,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2609290086</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="Q89" s="3" t="n">
@@ -5336,16 +5516,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3491</v>
+        <v>3591</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46308</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-11 14:54:07</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>DC2609280008 CP2609290086</t>
+          <t>CP2610110001</t>
         </is>
       </c>
       <c r="Q90" s="3" t="n">
@@ -5356,67 +5542,44 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>coupon voucher</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-002420</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3491</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>CP2609290086 CP2610110001 DC2609280008</t>
-        </is>
+        <v>3601</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>2610097EKRWPYW</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>CP2609290086 CP2610110001 DC2609280008</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>3491</v>
+        <v>46326</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-11 14:58:04</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>CP</t>
+          <t>2026-10-13 12:38:17</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>DC2609280008</t>
+          <t>CP2609290086</t>
         </is>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>46308</v>
+        <v>46326</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
         </is>
       </c>
     </row>
@@ -5427,17 +5590,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3591</v>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>46306</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46308</v>
+        <v>3491</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-11 14:53:51</t>
+          <t>2026-10-13 12:32:14</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -5460,125 +5617,7215 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MNL-002420</t>
+          <t>MNL-002484</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3601</v>
+        <v>4648</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>46296</v>
+        <v>46301.00001157408</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
+      </c>
+      <c r="G93" t="n">
+        <v>62</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>26101082C317K0</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>CP2610060002</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>4648</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-11 14:47:22</t>
+          <t>2026-10-11 17:27:26</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>OC</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>CP2609290086</t>
+          <t>CP2610060002</t>
         </is>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>46296</v>
+        <v>46301.00001157408</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>46326</v>
+        <v>46326.99998842592</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>ไม่มี pattern, cp/dcที่พบ: 2 อัน</t>
+          <t>Promotion xmn lg period 06-31 oct 2026 topup all store bg250024</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MNL-002511</t>
+          <t>MNL-001886</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3491</v>
+        <v>6579</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2610109PVC6G1R</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>6579</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-11 14:57:09</t>
+          <t>2026-10-12 10:48:05</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>CP2610110001</t>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MNL-002484</t>
+          <t>MNL-001886</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4648</v>
+        <v>6590</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CP2610060002</t>
+          <t>DC2609280008</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>261011AFXP2488</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>6590</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:49:36</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MNL-002522</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5493</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2610109UX6N87F</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>5493</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:44:14</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q96" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MNL-002382</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>11245</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>261012EAHYGF1R</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>11245</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:32:52</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MNL-002025</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>10940</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>261011BANBGRSQ</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>10940</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:31:49</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MNL-002194</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2929</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>261011B36FRGV5</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>2929</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:53:33</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MNL-002564</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3950</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>261011A559VK8W</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>3950</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:02:10</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MNL-002418</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2908</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>261011BTT460CW</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>2908</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:33:13</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R101" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MNL-002566</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3296</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>26101095H3APUU</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>3296</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:08:29</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R102" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MNL-002407</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3822</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>261012E802SEB4</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>3822</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:39:06</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q103" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R103" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MNL-002383</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>8434</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>261011BRDAHRPF</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>8434</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:37:48</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q104" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MNL-002450</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2438</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>261012EX6MBGSW</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>2438</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:41:29</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q105" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R105" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MNL-002486</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>6994</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>261011A48FNA89</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>6994</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:19:15</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q106" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R106" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MNL-002540</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>13848</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>261011BT0HXA4C</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>13848</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:40:51</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q107" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R107" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MNL-002529</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3786</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>261011CDP775Q2</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>3786</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:41:31</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="Q108" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MNL-002503</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7684</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>261011BC9YNWAN</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>7684</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:42:39</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>CP2609290070</t>
+        </is>
+      </c>
+      <c r="Q109" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R109" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MNL-002500</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>261011BER8YVT4</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>2900</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:43:24</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q110" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R110" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup), promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MNL-002568</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5110</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>261011A7QXFEDK</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>5110</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:37:20</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q111" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R111" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MNL-002551</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3047</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>261010A2CB68E6</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>3047</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:48:11</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q112" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R112" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MNL-002572</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>15094</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>261011ACK48PT0</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>15094</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:42:58</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q113" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R113" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MNL-002563</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2756</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2610109TMXPA94</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>2756</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:53:29</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q114" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R114" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MNL-002554</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2713</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2610107PS6KB0N</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>2713</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:59:32</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q115" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R115" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MNL-002400</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>5509</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>261011C697J2G2</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>5509</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:35:56</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="Q116" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R116" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung period 1-31 oct 26 topup all store bg250023, promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MNL-002553</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3739</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>261011AQ04J3RC</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>3739</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:37:22</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q117" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R117" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MNL-002574</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>5318</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>261011CFB4VD19</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>5318</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:51:29</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R118" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MNL-002528</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>38749</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2610109WRAA2WU</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>38749</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:11:10</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>CP2610010051</t>
+        </is>
+      </c>
+      <c r="Q119" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R119" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 01-15 oct 26 addon online (bg260024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MNL-002567</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3725</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>261010A2UCSMYU</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>3725</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:36:48</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q120" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R120" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MNL-002555</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>3532</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>261011A3DNCNTY</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>3532</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:46:30</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="Q121" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R121" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MNL-002384</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>11191</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>261011CE81FYNQ</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>11191</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:47:16</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="Q122" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R122" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung period 1-31 oct 26 topup all store bg250023, promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MNL-002559</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>4312</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2610109JQ9YXKQ</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>4312</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:14:40</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>CP2609290087</t>
+        </is>
+      </c>
+      <c r="Q123" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R123" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MNL-002500</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2896</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100001</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>261009703XVW4S</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>CP2610100001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>2896</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:43:19</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100001</t>
+        </is>
+      </c>
+      <c r="Q124" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R124" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2896</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MNL-002447</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>8139</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CP2609280033</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>261012CQVWD8YX</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>CP2609280033</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>8139</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:49:09</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>CP2609280033</t>
+        </is>
+      </c>
+      <c r="Q125" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R125" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung period 1-31 oct 26 topup all store bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AC2-001360</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>399</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>261011ACF0K5GC</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>399</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:04:54</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MNL-002482</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>25458</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CP2609290070 CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2610107QVU5UYK</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>CP2609290070 CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>25458</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:17:13</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290070 CP2610010051</t>
+        </is>
+      </c>
+      <c r="Q127" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R127" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup), promotion xmn lg period 01-15 oct 26 addon online (bg260024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MNL-002309</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>10195</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>261011BYF5JDYV</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>10195</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:34:31</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>CP2609280033 CP2609290087</t>
+        </is>
+      </c>
+      <c r="Q128" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R128" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>promotion xmn samsung period 1-31 oct 26 topup all store bg250023, promotion xmn samsung  period 1-31 oct 2026 addon online bg250023</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>5938</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>261012DVYV8X5Y</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>5938</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:15:02</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q129" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R129" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>5938</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:14:44</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PR6-000277</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>5207</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>261012DYSH037M</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>5207</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:16:34</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R131" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 5207</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2127</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>261012E0NP67EV</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>2127</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:17:32</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q132" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R132" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 2127</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2127</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:17:10</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>CP2610020012 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 2274</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2127</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:17:10</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610020012 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q134" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R134" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2127</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:17:10</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>8465</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>261012EB1N4SP2</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M136" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:24</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q136" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 8465</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q137" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R137" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>CP2610020012 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q138" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R138" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 8671</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>CP2610060006 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q139" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R139" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610020012 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q140" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R140" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610060006 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q141" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R141" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ราคาเซท 952</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>CP2610020012 CP2610060006 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q142" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R142" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PR5-000635</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>8465</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:04</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610020012 CP2610060006 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q143" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R143" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ราคาเซท 952</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PR2-000492</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3299</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:53:28</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>DC2609290041 DC2610070005</t>
+        </is>
+      </c>
+      <c r="Q144" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R144" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1603, Shp/TT เดือน ต.ค. ราคา 3299</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PR2-000492</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3299</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>261011BF2H1EX5</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>3299</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:53:38</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="Q145" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R145" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 3299</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4112</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CP2610060024</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>261012DPF2TGUX</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>CP2610060024</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>CP2610060024</t>
+        </is>
+      </c>
+      <c r="Q146" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R146" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>FS Shp ถูกชัวร์ 10.10 ราคา 4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610060024</t>
+        </is>
+      </c>
+      <c r="Q147" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R147" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ถูกชัวร์ 10.10 ราคา 4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>CP2610060006 CP2610060024</t>
+        </is>
+      </c>
+      <c r="Q148" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R148" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952, FS Shp ถูกชัวร์ 10.10 ราคา 4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>CP2610060024 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q149" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R149" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>FS Shp ถูกชัวร์ 10.10 ราคา 4112, Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610060006 CP2610060024</t>
+        </is>
+      </c>
+      <c r="Q150" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R150" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ราคาเซท 952, FS Shp ถูกชัวร์ 10.10 ราคา 4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610060024 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q151" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R151" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ถูกชัวร์ 10.10 ราคา 4112, Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>CP2610060006 CP2610060024 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q152" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R152" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952, FS Shp ถูกชัวร์ 10.10 ราคา 4112, Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4112</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:18:49</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610060006 CP2610060024 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q153" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974, FS Shp ราคาเซท 952, FS Shp ถูกชัวร์ 10.10 ราคา 4112, Shp/TT เดือน ต.ค. ราคา 5938</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PR5-000660</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>6330</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>261011B7AVXT17</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>6330</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:58:17</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q154" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R154" s="3" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PR5-000660</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>5495</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:55:58</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q155" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R155" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>4540</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>261011BDCD4J9R</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>4540</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00:40</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q156" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R156" s="3" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3575</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:01:23</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q157" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R157" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:21</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="n">
+        <v>46305.00001157408</v>
+      </c>
+      <c r="R158" s="3" t="n">
+        <v>46310.99998842592</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:22</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q159" s="3" t="n">
+        <v>46305.00001157408</v>
+      </c>
+      <c r="R159" s="3" t="n">
+        <v>46310.99998842592</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PR5-000661</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>8576</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>261011BH5WAHXX</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>8576</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:20:46</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q160" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R160" s="3" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PR5-000661</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>8576</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:20:25</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q161" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R161" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PR5-000661</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>8576</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:20:26</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>DC2610020005 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q162" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R162" s="3" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PR5-000661</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>8576</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:20:26</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>CP2609290081 DC2610020005 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R163" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>15327</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>261012EJJCXVUU</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:53</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q164" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R164" s="3" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q165" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R165" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>DC2610020005 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q166" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R166" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 17513</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q167" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="R167" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 15327</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>CP2609290081 DC2610020005 CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q168" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R168" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>CP2609290081 CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q169" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="R169" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>DC2610020005 CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q170" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="R170" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 17513</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PR6-000432</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>15327</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:20:36</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>CP2609290081 DC2610020005 CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q171" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="R171" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคาเซท 2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>10238</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CP2609300041 CP2610070014</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:23:17</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>CP2609300041 CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q172" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R172" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 10430</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>10238</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:23:17</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>CP2609300041 DC2610020004 CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R173" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 10430</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>10238</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:23:17</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>DC2610020004 CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q174" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R174" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Dynamic ต.ค. Shp ราคา 11180</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>14379</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>261013G6PG16DD</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>14379</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:27:30</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q175" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R175" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 14379</t>
+        </is>
+      </c>
+      <c r="T175" t="n">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PR5-000667</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>7067</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>261012E61TKCPY</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="M176" t="n">
+        <v>7067</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:29:38</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q176" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R176" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 7067</t>
+        </is>
+      </c>
+      <c r="T176" t="n">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PR5-000686</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>4885</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>261011BAUQM4N1</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
+        <v>4885</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30:12</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q177" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R177" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4885</t>
+        </is>
+      </c>
+      <c r="T177" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PR5-000686</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>4606</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CP2610060011</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>261012ENQRC32N</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>CP2610060011</t>
+        </is>
+      </c>
+      <c r="M178" t="n">
+        <v>4606</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30:36</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>CP2610060011</t>
+        </is>
+      </c>
+      <c r="Q178" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R178" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>FS Shp ราคา 4606</t>
+        </is>
+      </c>
+      <c r="T178" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PR5-000687</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5587</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>261012DU8P29M4</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="M179" t="n">
+        <v>5587</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:24:30</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R179" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 5587</t>
+        </is>
+      </c>
+      <c r="T179" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PR5-000680</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2633</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>261012DNXDT203</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="M180" t="n">
+        <v>2633</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:44:59</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>DC2610070005</t>
+        </is>
+      </c>
+      <c r="Q180" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R180" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 2633</t>
+        </is>
+      </c>
+      <c r="T180" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MNL-002445</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2906</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609280021</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="G181" t="n">
+        <v>59</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:28:16</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609280021</t>
+        </is>
+      </c>
+      <c r="Q181" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R181" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053</t>
+        </is>
+      </c>
+      <c r="T181" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MNL-002497</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610120003</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="G182" t="n">
+        <v>40</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:29:47</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 3 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MNL-002387</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2972</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G183" t="n">
+        <v>60</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:30:25</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R183" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T183" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>MNL-002435</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2793</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609280021</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="G184" t="n">
+        <v>57</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:31:05</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609280021</t>
+        </is>
+      </c>
+      <c r="Q184" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R184" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, Promotion xdt acer period 1-13 Oct 26 Topup All Store  BG250053</t>
+        </is>
+      </c>
+      <c r="T184" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MNL-002512</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>6822</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>261010A1AEV1EP</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
+        <v>6822</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:33:38</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R185" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MNL-002358</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>261011BJW898T8</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
+        <v>2202</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:35:05</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R186" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MNL-002419</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>3924</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>261011C445UW8V</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
+        <v>3924</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:36:27</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>CP2609290086 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R187" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157, promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MNL-002514</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5722</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>261011BF0CDYPB</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
+        <v>5722</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:39:59</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R188" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MNL-002584</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2065</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G189" t="n">
+        <v>42</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:44:14</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q189" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R189" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T189" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>MNL-002552</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>6801</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609300027</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G190" t="n">
+        <v>138</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:45:06</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609300027</t>
+        </is>
+      </c>
+      <c r="Q190" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R190" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, promotion xmn viewsonic period 1-31 oct 2026  topup all store (viewsonic sup)</t>
+        </is>
+      </c>
+      <c r="T190" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>MNL-002423</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>14933</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:45:49</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q191" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R191" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T191" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MNL-002478</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>3198</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>261011BE8AR7YY</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="M192" t="n">
+        <v>3198</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:48:41</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q192" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R192" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 3317 และปรับราคาขึ้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MNL-002544</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>11275</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:49:55</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R193" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T193" t="n">
+        <v>10510</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>MNL-002425</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3185</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:50:50</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 1 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>MNL-002562</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>9658</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>261011CJ5AQVN5</t>
+        </is>
+      </c>
+      <c r="M195" t="n">
+        <v>9658</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:51:54</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>MNL-002298</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>6717</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:52:49</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q196" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R196" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T196" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MNL-002569</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>3519</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:53:48</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q197" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R197" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T197" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CO6-011535</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>30600</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:54:28</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 6 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CO6-011852</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>25790</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CP2610050023 DC2410010001 DC2507220036</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
         <v>46301.00001157408</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E199" s="3" t="n">
+        <v>46334.99998842592</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>261012ETSQMJNS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>CP2610050023 DC2410010001 DC2507220036</t>
+        </is>
+      </c>
+      <c r="M199" t="n">
+        <v>25790</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:55:20</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>CP2610050023 DC2410010001 DC2507220036</t>
+        </is>
+      </c>
+      <c r="Q199" s="3" t="n">
+        <v>46301.00001157408</v>
+      </c>
+      <c r="R199" s="3" t="n">
+        <v>46334.99998842592</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Promotion MSI Notebook MSI Claw 06 Oct - 08 Nov 2026 (ตัด BG260022) (เฉพาะออนไลน์), DC MSI Notebook 2025, NOTEBOOK MSI : BUNDLE MOUSE WISE MT-202</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CO6-011797</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>31590</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CP2610050009 CP2610090005 CP2610090006 CP2610100010 DC2610050002 DC2410300012 DC2507220026</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>46305.00001157408</v>
+      </c>
+      <c r="E200" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
-      <c r="G95" t="n">
-        <v>62</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>26101082C317K0</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>CP2610060002</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
-        <v>4648</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>2026-10-11 17:27:26</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>261012F38FRYX1</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>CP2610050009 CP2610090005 CP2610090006 CP2610100010 DC2610050002 DC2410300012 DC2507220026</t>
+        </is>
+      </c>
+      <c r="M200" t="n">
+        <v>31590</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:55:46</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>CP2610050009 CP2610090005 CP2610090006 CP2610100010 DC2610050002 DC2410300012 DC2507220026</t>
+        </is>
+      </c>
+      <c r="Q200" s="3" t="n">
+        <v>46305.00001157408</v>
+      </c>
+      <c r="R200" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Promotion Support Sale Out Notebook HP Period 05 - 25 Oct '26 (NW), 27,990 / Push Sale Out, Support 2%, Promotion Support Sale Out Notebook HP Period 05 - 25 Oct '26 (DC), HP NOTEBOOK BUNDLE MOUSE (GMM-809/856) NUBWO NM106, NOTEBOOK HP : BUNDLE MOUSE WISE MT-202</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CO6-011653</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>22690</v>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:56:25</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 4 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CO6-011872</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>16930</v>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:57:04</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 1 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CO6-011927</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>76390</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:57:52</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 1 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CO6-011461</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>38410</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>DC2211290009 DC2507220016 DC2607020019 DC2610030003</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>261012EF3Q12DQ</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>DC2211290009 DC2507220016 DC2607020019 DC2610030003</t>
+        </is>
+      </c>
+      <c r="M204" t="n">
+        <v>38410</v>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:58:33</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
         <is>
           <t>OC</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>CP2610060002</t>
-        </is>
-      </c>
-      <c r="Q95" s="3" t="n">
-        <v>46301.00001157408</v>
-      </c>
-      <c r="R95" s="3" t="n">
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>DC2211290009 DC2507220016 DC2607020019 DC2610030003</t>
+        </is>
+      </c>
+      <c r="Q204" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R204" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Acer Promotion Notebook Period 2025, NOTEBOOK ACER : BUNDLE MOUSE WISE MT-202, DC CO6+COA Acer 02July-31Dec 2026, Promotion AIP Acer IP4-2442 แถมกับ NB Tech Playground 1-13 Oct 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CO3-001065</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>25802</v>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:59:16</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 5 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CO3-001063</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>28352</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:59:51</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q206" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R206" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T206" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PR1-000584</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1217</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00:41</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>DC2610070009</t>
+        </is>
+      </c>
+      <c r="Q207" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R207" s="3" t="n">
         <v>46326.99998842592</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Promotion xmn lg period 06-31 oct 2026 topup all store bg250024</t>
-        </is>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 1217</t>
+        </is>
+      </c>
+      <c r="T207" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2443</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:01:42</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q208" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R208" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PR5-000683</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1580</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:02:38</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>DC2610070009</t>
+        </is>
+      </c>
+      <c r="Q209" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="R209" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PR2-000495</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>4464</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:03:44</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q210" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R210" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T210" t="n">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PR5-000503</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2088</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:04:39</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q211" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R211" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T211" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PR5-000547</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>4411</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:05:31</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q212" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R212" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PR5-000631</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1695</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:06:24</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>DC2610100004</t>
+        </is>
+      </c>
+      <c r="Q213" s="3" t="n">
+        <v>46305.00001157408</v>
+      </c>
+      <c r="R213" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Shp ถูกชัวร์ ราคา 1695</t>
+        </is>
+      </c>
+      <c r="T213" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3054</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:07:19</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q214" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R214" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PR5-000646</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>4856</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:08:12</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q215" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R215" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PR5-000668</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>4914</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:09:14</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q216" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R216" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PR5-000677</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>4317</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:11:11</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q217" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R217" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PR5-000654</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>7079</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:11:52</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q218" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R218" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T218" t="n">
+        <v>3721</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PR5-000655</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>9114</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:12:42</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q219" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R219" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T219" t="n">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PR5-000673</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>7898</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:13:18</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q220" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R220" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T220" t="n">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PR6-000453</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>13443</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:14:10</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>CP2610070011</t>
+        </is>
+      </c>
+      <c r="Q221" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R221" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T221" t="n">
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PR6-000223</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>4323</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:15:38</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q222" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R222" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PR5-000658</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>3982</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:19:07</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>CP2610060006</t>
+        </is>
+      </c>
+      <c r="Q223" s="3" t="n">
+        <v>46302.00001157408</v>
+      </c>
+      <c r="R223" s="3" t="n">
+        <v>46315.99998842592</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>FS Shp ราคาเซท 952</t>
+        </is>
+      </c>
+      <c r="T223" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PR5-000549</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>24851</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:21:48</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q224" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R224" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="T224" t="n">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>PR5-000636</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>11291</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:22:40</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>CP2610070005</t>
+        </is>
+      </c>
+      <c r="Q225" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="R225" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="T225" t="n">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>PR5-000613</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>9536</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:25:43</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q226" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R226" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PR5-000642</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6798</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:26:33</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>DC2610070012</t>
+        </is>
+      </c>
+      <c r="Q227" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R227" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T227" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PR5-000670</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>11408</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:28:31</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>CP2610070014</t>
+        </is>
+      </c>
+      <c r="Q228" s="3" t="n">
+        <v>46304.00001157408</v>
+      </c>
+      <c r="R228" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>MNL-002578</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>3039</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>261012DTG81X3K</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>3039</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:31:05</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q229" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R229" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>MNL-002550</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>3039</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>261012DUMY19B4</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>3039</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:31:59</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>CP2610010047</t>
+        </is>
+      </c>
+      <c r="Q230" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R230" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>MNL-002265</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>3532</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:34:21</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609280028</t>
+        </is>
+      </c>
+      <c r="Q231" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R231" s="3" t="n">
+        <v>46308.99998842592</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, Promotion xmn acer  period 1-13 Oct 26 topup all store  IABP260665</t>
+        </is>
+      </c>
+      <c r="T231" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>MNL-002471</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>4167</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>261012EECTJRXT</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>4167</v>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:36:05</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q232" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R232" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>MNL-002390</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>2908</v>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:36:47</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q233" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R233" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T233" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>MNL-002381</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>5299</v>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:37:41</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 3 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>MNL-002287</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>6628</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>261012E6FFE1HU</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>6628</v>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:38:34</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>CP2609290070 DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q235" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R235" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup), promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>MNL-002475</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>8907</v>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:39:57</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610110001</t>
+        </is>
+      </c>
+      <c r="Q236" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R236" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T236" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>MNL-002532</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>6756</v>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:40:46</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q237" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R237" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+      <c r="T237" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>MNL-002489</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>2929</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>261012E4SXM2SF</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>2929</v>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:42:05</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>MNL-002412</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>2839</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>261012E36S58UY</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>2839</v>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:42:45</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q239" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R239" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>MNL-002470</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>5303</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>261012DY3SQX1V</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>5303</v>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:43:25</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q240" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R240" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MNL-002542</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>5426</v>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:44:23</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 3 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>MNL-002516</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>5238</v>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:45:13</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q242" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R242" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T242" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>MNL-002580</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2420</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>261012E65JQVJ9</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
+        <v>2420</v>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:45:51</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>MNL-002408</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3721</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>261012EFV6V8AR</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
+        <v>3721</v>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:46:34</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q244" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R244" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>MNL-002405</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4510</v>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:47:23</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="Q245" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R245" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand</t>
+        </is>
+      </c>
+      <c r="T245" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>MNL-002535</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>3890</v>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:48:13</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q246" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R246" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+      <c r="T246" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>MNL-002412</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2781</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CP2610100002 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>261012E36S58UY</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>DC2609280008</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
+        <v>2839</v>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:42:45</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q247" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R247" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>MNL-002478</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>3133</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>261011BE8AR7YY</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>3198</v>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:48:41</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q248" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R248" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 3317 และปรับราคาขึ้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>MNL-002552</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6801</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609300027</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:45:06</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609300027</t>
+        </is>
+      </c>
+      <c r="Q249" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R249" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, promotion xmn viewsonic period 1-31 oct 2026  topup all store (viewsonic sup)</t>
+        </is>
+      </c>
+      <c r="T249" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>MNL-002500</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2896</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>CP2610100001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>261009703XVW4S</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>CP2610100001 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M250" t="n">
+        <v>2896</v>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:43:19</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610100001</t>
+        </is>
+      </c>
+      <c r="Q250" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R250" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2896</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>MNL-002497</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610120003</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:29:47</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 3 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>MNL-002497</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>3567</v>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:29:47</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>ไม่มี pattern, cp/dcที่พบ: 3 อัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>MNL-002358</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2157</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>261011BJW898T8</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>CP2609290086</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>2202</v>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:35:05</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>CP2609290086 CP2610090037</t>
+        </is>
+      </c>
+      <c r="Q253" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R253" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2157</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>PR5-000659</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>4540</v>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:19:39</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>CP2610070005 CP2610090034</t>
+        </is>
+      </c>
+      <c r="Q254" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="R254" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Shp/TT เดือน ต.ค. ราคา 4540</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>MNL-002482</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>25458</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290070 CP2610010051</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2610107QVU5UYK</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>CP2609290070 CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>25458</v>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:17:13</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2609290070 CP2610010051</t>
+        </is>
+      </c>
+      <c r="Q255" s="3" t="n">
+        <v>46296.00001157408</v>
+      </c>
+      <c r="R255" s="3" t="n">
+        <v>46326.99998842592</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>promotion xdt xmn period 01-31 oct 2026 topup all store dc months all brand, promotion xmn lg period 1-31 Oct 2026 topup all store (lg sup), promotion xmn lg period 01-15 oct 26 addon online (bg260024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>MNL-002528</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>38749</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>DC2609280008 CP2610010051</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2610109WRAA2WU</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>CP2610010051 DC2609280008</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>38749</v>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:11:10</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>CP2610010051</t>
+        </is>
+      </c>
+      <c r="Q256" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="R256" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>promotion xmn lg period 01-15 oct 26 addon online (bg260024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>MNL-002531</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>5590</v>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:49:40</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>CP2610100002</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>ใช้คูปอง dynamic นี้ราคาขายยิงขึ้น 2187</t>
+        </is>
+      </c>
+      <c r="T257" t="n">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S95"/>
+  <autoFilter ref="A1:V257"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>